--- a/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
+++ b/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
@@ -26,6 +26,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'C_jama.2024.24764'!$A$1:$R$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'C_jama.2024.27643'!$A$1:$R$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'C_jama.2025.11178'!$A$1:$R$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'C_jama.2025.15185'!$A$1:$R$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'C_jama.2025.15440'!$A$1:$R$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'C_jama.2025.16450'!$A$1:$R$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'C_jama.2025.19563'!$A$1:$R$14</definedName>
@@ -129,7 +131,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
@@ -226,7 +228,6 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -8656,7 +8657,7 @@
         </is>
       </c>
       <c r="B3" s="17" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" ht="55" customFormat="1" customHeight="1" s="14">
@@ -8666,7 +8667,7 @@
         </is>
       </c>
       <c r="B4" s="16">
-        <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
+        <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.11178'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2025.15185'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
         <v/>
       </c>
     </row>
@@ -8677,7 +8678,7 @@
         </is>
       </c>
       <c r="B5" s="17">
-        <f>COUNTIF('C_jama.2024.24764'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2024.27643'!$D$2:$D$17,"discuss")+COUNTIF('C_jama.2025.15440'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2025.16450'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.19563'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.19843'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2025.20765'!$D$2:$D$20,"discuss")+COUNTIF('C_jama.2025.24175'!$D$2:$D$15,"discuss")+COUNTIF('C_jama.2025.4390'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.7583'!$D$2:$D$5,"discuss")+COUNTIF('C_jama.2025.7710'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9110'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9663'!$D$2:$D$6,"discuss")</f>
+        <f>COUNTIF('C_jama.2024.24764'!$D$2:$D$6,"discuss")+COUNTIF('C_jama.2024.27643'!$D$2:$D$17,"discuss")+COUNTIF('C_jama.2025.11178'!$D$2:$D$19,"discuss")+COUNTIF('C_jama.2025.15185'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.15440'!$D$2:$D$2,"discuss")+COUNTIF('C_jama.2025.16450'!$D$2:$D$7,"discuss")+COUNTIF('C_jama.2025.19563'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.19843'!$D$2:$D$8,"discuss")+COUNTIF('C_jama.2025.20765'!$D$2:$D$20,"discuss")+COUNTIF('C_jama.2025.24175'!$D$2:$D$15,"discuss")+COUNTIF('C_jama.2025.4390'!$D$2:$D$14,"discuss")+COUNTIF('C_jama.2025.7583'!$D$2:$D$5,"discuss")+COUNTIF('C_jama.2025.7710'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9110'!$D$2:$D$4,"discuss")+COUNTIF('C_jama.2025.9663'!$D$2:$D$6,"discuss")</f>
         <v/>
       </c>
     </row>
@@ -8738,13 +8739,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" style="14" min="1" max="1"/>
     <col width="38" customWidth="1" style="14" min="2" max="2"/>
     <col width="18" customWidth="1" style="14" min="3" max="3"/>
-    <col width="60" customWidth="1" style="25" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customFormat="1" customHeight="1" s="14">
@@ -8763,11 +8763,6 @@
           <t>Candidates</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
     </row>
     <row r="2" ht="36" customHeight="1" s="25">
       <c r="A2" s="16" t="inlineStr">
@@ -8811,12 +8806,7 @@
         </is>
       </c>
       <c r="C4" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Placeholder: workflow 1.6.2 output pending; no candidates in this version</t>
-        </is>
+        <v>18</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" s="25">
@@ -8831,12 +8821,7 @@
         </is>
       </c>
       <c r="C5" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>Placeholder: workflow 1.6.2 output pending; no candidates in this version</t>
-        </is>
+        <v>6</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" s="25">
@@ -10559,7 +10544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="14" min="1" max="1"/>
@@ -10654,14 +10639,1108 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Placeholder: no workflow 1.6.2 output for this paper yet; nothing to review in v.2.4.1.</t>
-        </is>
-      </c>
+    <row r="2" ht="92" customHeight="1" s="25">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>Planned versus reported online session duration</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>Yes, all five locations: REPORT main p.3, Health Coach Program and Online Program — jama_debar_2025_oi_250046_1755300121.13587.pdf; PLAN protocol p.43 §10.1.1 — joi250046supp1_prod_1755300121.14087.pdf and p.44 coach overview — joi250046supp1_prod_1755300121.14087.pdf; REPORT TIDieR p.3 Procedures — joi250046supp3_prod_1755300121.15087.pdf and p.4 When and How Much — joi250046supp3_prod_1755300121.15087.pdf.</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G2" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$19,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M2" s="20" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="92" customHeight="1" s="25">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C002</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Therapeutic-dose adherence percentage</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 Results adherence paragraph — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.5 Figure 1 PT allocation/session counts — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G3" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$19,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="92" customHeight="1" s="25">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>SMD construction across Table 3</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 SMD definition — jama_debar_2025_oi_250046_1755300121.13587.pdf, p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf, and p.11 continuation and footnote d — jama_debar_2025_oi_250046_1755300121.13587.pdf. All twenty registered outcome/time rows and all three point-contrast columns per row were read directly.</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G4" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$19,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="22" t="n"/>
+    </row>
+    <row r="5" ht="92" customHeight="1" s="25">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C004</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Reciprocal NNT point-reproduction pattern</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.4 NNT definition — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT main p.9 Table 2 severity 6-month HC/UC, interference 6-month HC/UC and footnote d — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.14 eTable 8 reminder-letter 6-month PT/UC and footnote d — joi250046supp4_prod_1755300121.15587.pdf. All three affected rows were read.</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$19,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="92" customHeight="1" s="25">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Age as a prespecified base adjustment covariate</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Yes: PLAN protocol p.56 §15.5 — joi250046supp1_prod_1755300121.14087.pdf; PLAN SAP p.20 §§13–14 — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 adjustment sentence — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.4 Adjustment — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 all-model variables — joi250046supp4_prod_1755300121.15587.pdf, p.8 eTable 3 age — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 age — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 age — joi250046supp4_prod_1755300121.15587.pdf; REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells G2, A10, G10, directly decoded.</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G6" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$19,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="22" t="n"/>
+    </row>
+    <row r="7" ht="92" customHeight="1" s="25">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C006</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Secondary-analysis adjustment specification</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>Yes: PLAN protocol p.57 §15.6 — joi250046supp1_prod_1755300121.14087.pdf; PLAN SAP p.21 §15 — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 secondary methods — jama_debar_2025_oi_250046_1755300121.13587.pdf, p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.11 continuation — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$19,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="22" t="n"/>
+    </row>
+    <row r="8" ht="92" customHeight="1" s="25">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C007</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>Primary versus sensitivity missing-data analysis roles</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Yes: PLAN SAP p.19 §11 — joi250046supp2_prod_1755300121.15087.pdf, PLAN p.4 July 17, 2024 amendment — joi250046supp2_prod_1755300121.15087.pdf; REPORT main p.4 missing-data paragraph — jama_debar_2025_oi_250046_1755300121.13587.pdf; REPORT results p.4 Missing Data — joi250046supp4_prod_1755300121.15587.pdf, p.5 Non-Response Weighting — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 — joi250046supp4_prod_1755300121.15587.pdf, p.11 sensitivity narrative and complete-case block — joi250046supp4_prod_1755300121.15587.pdf. P.5 was read as disclosed-amendment context in addition to the registered comparisons.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="n"/>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G8" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$19,A8)&lt;&gt;1,LEFT(A8,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J8" s="22">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>IF(AND(OR(D8="retain",D8=""),OR(E8="report_internal_inconsistency",E8="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L8" s="22">
+        <f>IF(AND(OR(D8="retain",D8=""),E8="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="23" t="n"/>
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="92" customHeight="1" s="25">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C008</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>RR versus finite NNT null coverage</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.9 Table 2 HC/PT columns and footnotes b,d,e — jama_debar_2025_oi_250046_1755300121.13587.pdf, all six registered contrast/time rows; REPORT p.4 binary model and NNT method — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="n"/>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G9" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$19,A9)&lt;&gt;1,LEFT(A9,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J9" s="22">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K9" s="21">
+        <f>IF(AND(OR(D9="retain",D9=""),OR(E9="report_internal_inconsistency",E9="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L9" s="22">
+        <f>IF(AND(OR(D9="retain",D9=""),E9="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M9" s="24" t="n"/>
+      <c r="N9" s="23" t="n"/>
+      <c r="O9" s="23" t="n"/>
+      <c r="P9" s="23" t="n"/>
+      <c r="Q9" s="23" t="n"/>
+      <c r="R9" s="22" t="n"/>
+    </row>
+    <row r="10" ht="92" customHeight="1" s="25">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C009</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>NNT point outside its confidence interval</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.9 Table 2 pain intensity 12 months, HC/PT NNT column — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n"/>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A10="",COUNTIF($A$2:$A$19,A10)&lt;&gt;1,LEFT(A10,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D10="retain",E10="statistical_results")),H10&lt;&gt;"",NOT(EXACT(H10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),I10&lt;&gt;"",NOT(EXACT(I10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),J10&lt;&gt;"",NOT(EXACT(J10,"not_applicable"))),AND(NOT(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material"))),K10&lt;&gt;"",NOT(EXACT(K10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="protocol_report")),L10&lt;&gt;"",NOT(EXACT(L10,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D10,"retain"),EXACT(D10,"exclude"),EXACT(D10,"discuss"))),NOT(OR(EXACT(E10,"statistical_results"),EXACT(E10,"report_internal_inconsistency"),EXACT(E10,"plan_material"),EXACT(E10,"protocol_report"))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(H10,"confirmed_issue"),EXACT(H10,"probable_issue"),EXACT(H10,"not_issue"),EXACT(H10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(I10,"substantive"),EXACT(I10,"minor_presentation"),EXACT(I10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),J10&lt;&gt;"",NOT(OR(EXACT(J10,"direct"),EXACT(J10,"possible"),EXACT(J10,"unlikely"),EXACT(J10,"unknown")))),AND(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material")),NOT(OR(EXACT(K10,"substantive_inconsistency"),EXACT(K10,"minor_presentation"),EXACT(K10,"non_inconsistency"),EXACT(K10,"indeterminate")))),AND(AND(D10="retain",E10="protocol_report"),L10&lt;&gt;"",NOT(OR(EXACT(L10,"substantive_difference"),EXACT(L10,"minor_presentation"),EXACT(L10,"version_timing"),EXACT(L10,"non_inconsistency"),EXACT(L10,"indeterminate"))))),"CHECK FIELDS",IF(AND(F10&lt;&gt;"",NOT(OR(EXACT(F10,"no"),EXACT(F10,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F10,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J10" s="22">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K10" s="21">
+        <f>IF(AND(OR(D10="retain",D10=""),OR(E10="report_internal_inconsistency",E10="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L10" s="22">
+        <f>IF(AND(OR(D10="retain",D10=""),E10="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="23" t="n"/>
+      <c r="O10" s="23" t="n"/>
+      <c r="P10" s="23" t="n"/>
+      <c r="Q10" s="23" t="n"/>
+      <c r="R10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="92" customHeight="1" s="25">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C010</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>SMD points outside printed confidence intervals</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT main p.10 Table 3 — jama_debar_2025_oi_250046_1755300121.13587.pdf and p.11 PGIC-pain continuation — jama_debar_2025_oi_250046_1755300121.13587.pdf. Every one of the fourteen registered tuples was read directly; all matched the ledger.</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G11" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A11="",COUNTIF($A$2:$A$19,A11)&lt;&gt;1,LEFT(A11,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D11="retain",E11="statistical_results")),H11&lt;&gt;"",NOT(EXACT(H11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),I11&lt;&gt;"",NOT(EXACT(I11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),J11&lt;&gt;"",NOT(EXACT(J11,"not_applicable"))),AND(NOT(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material"))),K11&lt;&gt;"",NOT(EXACT(K11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="protocol_report")),L11&lt;&gt;"",NOT(EXACT(L11,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D11,"retain"),EXACT(D11,"exclude"),EXACT(D11,"discuss"))),NOT(OR(EXACT(E11,"statistical_results"),EXACT(E11,"report_internal_inconsistency"),EXACT(E11,"plan_material"),EXACT(E11,"protocol_report"))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(H11,"confirmed_issue"),EXACT(H11,"probable_issue"),EXACT(H11,"not_issue"),EXACT(H11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(I11,"substantive"),EXACT(I11,"minor_presentation"),EXACT(I11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),J11&lt;&gt;"",NOT(OR(EXACT(J11,"direct"),EXACT(J11,"possible"),EXACT(J11,"unlikely"),EXACT(J11,"unknown")))),AND(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material")),NOT(OR(EXACT(K11,"substantive_inconsistency"),EXACT(K11,"minor_presentation"),EXACT(K11,"non_inconsistency"),EXACT(K11,"indeterminate")))),AND(AND(D11="retain",E11="protocol_report"),L11&lt;&gt;"",NOT(OR(EXACT(L11,"substantive_difference"),EXACT(L11,"minor_presentation"),EXACT(L11,"version_timing"),EXACT(L11,"non_inconsistency"),EXACT(L11,"indeterminate"))))),"CHECK FIELDS",IF(AND(F11&lt;&gt;"",NOT(OR(EXACT(F11,"no"),EXACT(F11,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F11,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J11" s="22">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>IF(AND(OR(D11="retain",D11=""),OR(E11="report_internal_inconsistency",E11="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L11" s="22">
+        <f>IF(AND(OR(D11="retain",D11=""),E11="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M11" s="24" t="n"/>
+      <c r="N11" s="23" t="n"/>
+      <c r="O11" s="23" t="n"/>
+      <c r="P11" s="23" t="n"/>
+      <c r="Q11" s="23" t="n"/>
+      <c r="R11" s="22" t="n"/>
+    </row>
+    <row r="12" ht="92" customHeight="1" s="25">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C011</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>Covariate set of restricted primary analyses</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.4 Adjustment — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 final imputation/estimation set — joi250046supp4_prod_1755300121.15587.pdf, p.13 Protocol Change Subset Analyses — joi250046supp4_prod_1755300121.15587.pdf, p.14 eTable 8 all three blocks and footnote b — joi250046supp4_prod_1755300121.15587.pdf. Fitted education/employment terms at p.8 — joi250046supp4_prod_1755300121.15587.pdf and p.9 — joi250046supp4_prod_1755300121.15587.pdf were also read as corroboration.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A12="",COUNTIF($A$2:$A$19,A12)&lt;&gt;1,LEFT(A12,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D12="retain",E12="statistical_results")),H12&lt;&gt;"",NOT(EXACT(H12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),I12&lt;&gt;"",NOT(EXACT(I12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),J12&lt;&gt;"",NOT(EXACT(J12,"not_applicable"))),AND(NOT(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material"))),K12&lt;&gt;"",NOT(EXACT(K12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="protocol_report")),L12&lt;&gt;"",NOT(EXACT(L12,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D12,"retain"),EXACT(D12,"exclude"),EXACT(D12,"discuss"))),NOT(OR(EXACT(E12,"statistical_results"),EXACT(E12,"report_internal_inconsistency"),EXACT(E12,"plan_material"),EXACT(E12,"protocol_report"))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(H12,"confirmed_issue"),EXACT(H12,"probable_issue"),EXACT(H12,"not_issue"),EXACT(H12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(I12,"substantive"),EXACT(I12,"minor_presentation"),EXACT(I12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),J12&lt;&gt;"",NOT(OR(EXACT(J12,"direct"),EXACT(J12,"possible"),EXACT(J12,"unlikely"),EXACT(J12,"unknown")))),AND(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material")),NOT(OR(EXACT(K12,"substantive_inconsistency"),EXACT(K12,"minor_presentation"),EXACT(K12,"non_inconsistency"),EXACT(K12,"indeterminate")))),AND(AND(D12="retain",E12="protocol_report"),L12&lt;&gt;"",NOT(OR(EXACT(L12,"substantive_difference"),EXACT(L12,"minor_presentation"),EXACT(L12,"version_timing"),EXACT(L12,"non_inconsistency"),EXACT(L12,"indeterminate"))))),"CHECK FIELDS",IF(AND(F12&lt;&gt;"",NOT(OR(EXACT(F12,"no"),EXACT(F12,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F12,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J12" s="22">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>IF(AND(OR(D12="retain",D12=""),OR(E12="report_internal_inconsistency",E12="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L12" s="22">
+        <f>IF(AND(OR(D12="retain",D12=""),E12="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="23" t="n"/>
+      <c r="O12" s="23" t="n"/>
+      <c r="P12" s="23" t="n"/>
+      <c r="Q12" s="23" t="n"/>
+      <c r="R12" s="22" t="n"/>
+    </row>
+    <row r="13" ht="92" customHeight="1" s="25">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C012</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>Final response-weight model predictor membership</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.4 Adjustment/selection — joi250046supp4_prod_1755300121.15587.pdf, p.5 Non-Response Weighting — joi250046supp4_prod_1755300121.15587.pdf, p.7 eTable 2 final nonresponse predictors — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 full coefficient display — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells A18, H18, I18, J18.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G13" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A13="",COUNTIF($A$2:$A$19,A13)&lt;&gt;1,LEFT(A13,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D13="retain",E13="statistical_results")),H13&lt;&gt;"",NOT(EXACT(H13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),I13&lt;&gt;"",NOT(EXACT(I13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),J13&lt;&gt;"",NOT(EXACT(J13,"not_applicable"))),AND(NOT(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material"))),K13&lt;&gt;"",NOT(EXACT(K13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="protocol_report")),L13&lt;&gt;"",NOT(EXACT(L13,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D13,"retain"),EXACT(D13,"exclude"),EXACT(D13,"discuss"))),NOT(OR(EXACT(E13,"statistical_results"),EXACT(E13,"report_internal_inconsistency"),EXACT(E13,"plan_material"),EXACT(E13,"protocol_report"))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(H13,"confirmed_issue"),EXACT(H13,"probable_issue"),EXACT(H13,"not_issue"),EXACT(H13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(I13,"substantive"),EXACT(I13,"minor_presentation"),EXACT(I13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),J13&lt;&gt;"",NOT(OR(EXACT(J13,"direct"),EXACT(J13,"possible"),EXACT(J13,"unlikely"),EXACT(J13,"unknown")))),AND(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material")),NOT(OR(EXACT(K13,"substantive_inconsistency"),EXACT(K13,"minor_presentation"),EXACT(K13,"non_inconsistency"),EXACT(K13,"indeterminate")))),AND(AND(D13="retain",E13="protocol_report"),L13&lt;&gt;"",NOT(OR(EXACT(L13,"substantive_difference"),EXACT(L13,"minor_presentation"),EXACT(L13,"version_timing"),EXACT(L13,"non_inconsistency"),EXACT(L13,"indeterminate"))))),"CHECK FIELDS",IF(AND(F13&lt;&gt;"",NOT(OR(EXACT(F13,"no"),EXACT(F13,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F13,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J13" s="22">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K13" s="21">
+        <f>IF(AND(OR(D13="retain",D13=""),OR(E13="report_internal_inconsistency",E13="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L13" s="22">
+        <f>IF(AND(OR(D13="retain",D13=""),E13="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M13" s="24" t="n"/>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="23" t="n"/>
+      <c r="R13" s="22" t="n"/>
+    </row>
+    <row r="14" ht="92" customHeight="1" s="25">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C013</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>Education coding and coefficient attribution</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.7 eTable 2 final primary predictor list — joi250046supp4_prod_1755300121.15587.pdf, p.8 eTable 3 all three education rows — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 all three education rows — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet eTable 3, cells A12:A16.</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A14="",COUNTIF($A$2:$A$19,A14)&lt;&gt;1,LEFT(A14,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D14="retain",E14="statistical_results")),H14&lt;&gt;"",NOT(EXACT(H14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),I14&lt;&gt;"",NOT(EXACT(I14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),J14&lt;&gt;"",NOT(EXACT(J14,"not_applicable"))),AND(NOT(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material"))),K14&lt;&gt;"",NOT(EXACT(K14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="protocol_report")),L14&lt;&gt;"",NOT(EXACT(L14,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D14,"retain"),EXACT(D14,"exclude"),EXACT(D14,"discuss"))),NOT(OR(EXACT(E14,"statistical_results"),EXACT(E14,"report_internal_inconsistency"),EXACT(E14,"plan_material"),EXACT(E14,"protocol_report"))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(H14,"confirmed_issue"),EXACT(H14,"probable_issue"),EXACT(H14,"not_issue"),EXACT(H14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(I14,"substantive"),EXACT(I14,"minor_presentation"),EXACT(I14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),J14&lt;&gt;"",NOT(OR(EXACT(J14,"direct"),EXACT(J14,"possible"),EXACT(J14,"unlikely"),EXACT(J14,"unknown")))),AND(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material")),NOT(OR(EXACT(K14,"substantive_inconsistency"),EXACT(K14,"minor_presentation"),EXACT(K14,"non_inconsistency"),EXACT(K14,"indeterminate")))),AND(AND(D14="retain",E14="protocol_report"),L14&lt;&gt;"",NOT(OR(EXACT(L14,"substantive_difference"),EXACT(L14,"minor_presentation"),EXACT(L14,"version_timing"),EXACT(L14,"non_inconsistency"),EXACT(L14,"indeterminate"))))),"CHECK FIELDS",IF(AND(F14&lt;&gt;"",NOT(OR(EXACT(F14,"no"),EXACT(F14,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F14,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J14" s="22">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K14" s="21">
+        <f>IF(AND(OR(D14="retain",D14=""),OR(E14="report_internal_inconsistency",E14="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L14" s="22">
+        <f>IF(AND(OR(D14="retain",D14=""),E14="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M14" s="20" t="n"/>
+      <c r="N14" s="23" t="n"/>
+      <c r="O14" s="23" t="n"/>
+      <c r="P14" s="23" t="n"/>
+      <c r="Q14" s="23" t="n"/>
+      <c r="R14" s="22" t="n"/>
+    </row>
+    <row r="15" ht="92" customHeight="1" s="25">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C014</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>Coefficient CI versus P-value null-significance pattern</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.8 eTable 3 seven registered rows — joi250046supp4_prod_1755300121.15587.pdf, p.9 eTable 4 age and second AA rows — joi250046supp4_prod_1755300121.15587.pdf, p.10 eTable 5 PEG row — joi250046supp4_prod_1755300121.15587.pdf. Method context was read at results p.4 — joi250046supp4_prod_1755300121.15587.pdf, p.5 — joi250046supp4_prod_1755300121.15587.pdf, and REPORT main p.4 two-sided alpha=.05 — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G15" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A15="",COUNTIF($A$2:$A$19,A15)&lt;&gt;1,LEFT(A15,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D15="retain",E15="statistical_results")),H15&lt;&gt;"",NOT(EXACT(H15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),I15&lt;&gt;"",NOT(EXACT(I15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="statistical_results")),J15&lt;&gt;"",NOT(EXACT(J15,"not_applicable"))),AND(NOT(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material"))),K15&lt;&gt;"",NOT(EXACT(K15,"not_applicable"))),AND(NOT(AND(D15="retain",E15="protocol_report")),L15&lt;&gt;"",NOT(EXACT(L15,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D15,"retain"),EXACT(D15,"exclude"),EXACT(D15,"discuss"))),NOT(OR(EXACT(E15,"statistical_results"),EXACT(E15,"report_internal_inconsistency"),EXACT(E15,"plan_material"),EXACT(E15,"protocol_report"))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(H15,"confirmed_issue"),EXACT(H15,"probable_issue"),EXACT(H15,"not_issue"),EXACT(H15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),NOT(OR(EXACT(I15,"substantive"),EXACT(I15,"minor_presentation"),EXACT(I15,"indeterminate")))),AND(AND(D15="retain",E15="statistical_results"),J15&lt;&gt;"",NOT(OR(EXACT(J15,"direct"),EXACT(J15,"possible"),EXACT(J15,"unlikely"),EXACT(J15,"unknown")))),AND(AND(D15="retain",OR(E15="report_internal_inconsistency",E15="plan_material")),NOT(OR(EXACT(K15,"substantive_inconsistency"),EXACT(K15,"minor_presentation"),EXACT(K15,"non_inconsistency"),EXACT(K15,"indeterminate")))),AND(AND(D15="retain",E15="protocol_report"),L15&lt;&gt;"",NOT(OR(EXACT(L15,"substantive_difference"),EXACT(L15,"minor_presentation"),EXACT(L15,"version_timing"),EXACT(L15,"non_inconsistency"),EXACT(L15,"indeterminate"))))),"CHECK FIELDS",IF(AND(F15&lt;&gt;"",NOT(OR(EXACT(F15,"no"),EXACT(F15,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F15,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J15" s="22">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K15" s="21">
+        <f>IF(AND(OR(D15="retain",D15=""),OR(E15="report_internal_inconsistency",E15="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L15" s="22">
+        <f>IF(AND(OR(D15="retain",D15=""),E15="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M15" s="24" t="n"/>
+      <c r="N15" s="23" t="n"/>
+      <c r="O15" s="23" t="n"/>
+      <c r="P15" s="23" t="n"/>
+      <c r="Q15" s="23" t="n"/>
+      <c r="R15" s="22" t="n"/>
+    </row>
+    <row r="16" ht="92" customHeight="1" s="25">
+      <c r="A16" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C015</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>Within-header three-month subset counts</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.14 eTable 8 first subgroup header — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT p.7 eTable 1 — joi250046supp4_prod_1755300121.15587.pdf, p.13 subset definition — joi250046supp4_prod_1755300121.15587.pdf, and the second/third headers on p.14.</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="n"/>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A16="",COUNTIF($A$2:$A$19,A16)&lt;&gt;1,LEFT(A16,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D16="retain",E16="statistical_results")),H16&lt;&gt;"",NOT(EXACT(H16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),I16&lt;&gt;"",NOT(EXACT(I16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="statistical_results")),J16&lt;&gt;"",NOT(EXACT(J16,"not_applicable"))),AND(NOT(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material"))),K16&lt;&gt;"",NOT(EXACT(K16,"not_applicable"))),AND(NOT(AND(D16="retain",E16="protocol_report")),L16&lt;&gt;"",NOT(EXACT(L16,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D16,"retain"),EXACT(D16,"exclude"),EXACT(D16,"discuss"))),NOT(OR(EXACT(E16,"statistical_results"),EXACT(E16,"report_internal_inconsistency"),EXACT(E16,"plan_material"),EXACT(E16,"protocol_report"))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(H16,"confirmed_issue"),EXACT(H16,"probable_issue"),EXACT(H16,"not_issue"),EXACT(H16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),NOT(OR(EXACT(I16,"substantive"),EXACT(I16,"minor_presentation"),EXACT(I16,"indeterminate")))),AND(AND(D16="retain",E16="statistical_results"),J16&lt;&gt;"",NOT(OR(EXACT(J16,"direct"),EXACT(J16,"possible"),EXACT(J16,"unlikely"),EXACT(J16,"unknown")))),AND(AND(D16="retain",OR(E16="report_internal_inconsistency",E16="plan_material")),NOT(OR(EXACT(K16,"substantive_inconsistency"),EXACT(K16,"minor_presentation"),EXACT(K16,"non_inconsistency"),EXACT(K16,"indeterminate")))),AND(AND(D16="retain",E16="protocol_report"),L16&lt;&gt;"",NOT(OR(EXACT(L16,"substantive_difference"),EXACT(L16,"minor_presentation"),EXACT(L16,"version_timing"),EXACT(L16,"non_inconsistency"),EXACT(L16,"indeterminate"))))),"CHECK FIELDS",IF(AND(F16&lt;&gt;"",NOT(OR(EXACT(F16,"no"),EXACT(F16,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F16,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J16" s="22">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K16" s="21">
+        <f>IF(AND(OR(D16="retain",D16=""),OR(E16="report_internal_inconsistency",E16="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L16" s="22">
+        <f>IF(AND(OR(D16="retain",D16=""),E16="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M16" s="20" t="n"/>
+      <c r="N16" s="23" t="n"/>
+      <c r="O16" s="23" t="n"/>
+      <c r="P16" s="23" t="n"/>
+      <c r="Q16" s="23" t="n"/>
+      <c r="R16" s="22" t="n"/>
+    </row>
+    <row r="17" ht="92" customHeight="1" s="25">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C016</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>Raw-score summary statistic and bounds in eTable 11</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Yes: REPORT results p.15 Additional Unadjusted Data and Analyses — joi250046supp4_prod_1755300121.15587.pdf, p.17 eTable 11 title/header and all 21 rows — joi250046supp4_prod_1755300121.15587.pdf, p.18 note b — joi250046supp4_prod_1755300121.15587.pdf; corroborating REPORT main p.11 PGIC footnotes h/i — jama_debar_2025_oi_250046_1755300121.13587.pdf.</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G17" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A17="",COUNTIF($A$2:$A$19,A17)&lt;&gt;1,LEFT(A17,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D17="retain",E17="statistical_results")),H17&lt;&gt;"",NOT(EXACT(H17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),I17&lt;&gt;"",NOT(EXACT(I17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),J17&lt;&gt;"",NOT(EXACT(J17,"not_applicable"))),AND(NOT(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material"))),K17&lt;&gt;"",NOT(EXACT(K17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="protocol_report")),L17&lt;&gt;"",NOT(EXACT(L17,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D17,"retain"),EXACT(D17,"exclude"),EXACT(D17,"discuss"))),NOT(OR(EXACT(E17,"statistical_results"),EXACT(E17,"report_internal_inconsistency"),EXACT(E17,"plan_material"),EXACT(E17,"protocol_report"))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(H17,"confirmed_issue"),EXACT(H17,"probable_issue"),EXACT(H17,"not_issue"),EXACT(H17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(I17,"substantive"),EXACT(I17,"minor_presentation"),EXACT(I17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),J17&lt;&gt;"",NOT(OR(EXACT(J17,"direct"),EXACT(J17,"possible"),EXACT(J17,"unlikely"),EXACT(J17,"unknown")))),AND(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material")),NOT(OR(EXACT(K17,"substantive_inconsistency"),EXACT(K17,"minor_presentation"),EXACT(K17,"non_inconsistency"),EXACT(K17,"indeterminate")))),AND(AND(D17="retain",E17="protocol_report"),L17&lt;&gt;"",NOT(OR(EXACT(L17,"substantive_difference"),EXACT(L17,"minor_presentation"),EXACT(L17,"version_timing"),EXACT(L17,"non_inconsistency"),EXACT(L17,"indeterminate"))))),"CHECK FIELDS",IF(AND(F17&lt;&gt;"",NOT(OR(EXACT(F17,"no"),EXACT(F17,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F17,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J17" s="22">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K17" s="21">
+        <f>IF(AND(OR(D17="retain",D17=""),OR(E17="report_internal_inconsistency",E17="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L17" s="22">
+        <f>IF(AND(OR(D17="retain",D17=""),E17="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M17" s="24" t="n"/>
+      <c r="N17" s="23" t="n"/>
+      <c r="O17" s="23" t="n"/>
+      <c r="P17" s="23" t="n"/>
+      <c r="Q17" s="23" t="n"/>
+      <c r="R17" s="22" t="n"/>
+    </row>
+    <row r="18" ht="92" customHeight="1" s="25">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C017</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Workbook All Observed depression percentage</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Yes: supplied REPORT workbook — joi250046supp5_prod_1755300121.16087.xlsx, worksheet exactly eTable 3, E3, A82, E82, A83, E83, A110. Direct workbook.xml confirms worksheet name and worksheet relationship; direct sheet1.xml/sharedStrings.xml confirms all cells. B82/C82/D82 were also read as count-partition corroboration.</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G18" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A18="",COUNTIF($A$2:$A$19,A18)&lt;&gt;1,LEFT(A18,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D18="retain",E18="statistical_results")),H18&lt;&gt;"",NOT(EXACT(H18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),I18&lt;&gt;"",NOT(EXACT(I18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),J18&lt;&gt;"",NOT(EXACT(J18,"not_applicable"))),AND(NOT(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material"))),K18&lt;&gt;"",NOT(EXACT(K18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="protocol_report")),L18&lt;&gt;"",NOT(EXACT(L18,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D18,"retain"),EXACT(D18,"exclude"),EXACT(D18,"discuss"))),NOT(OR(EXACT(E18,"statistical_results"),EXACT(E18,"report_internal_inconsistency"),EXACT(E18,"plan_material"),EXACT(E18,"protocol_report"))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(H18,"confirmed_issue"),EXACT(H18,"probable_issue"),EXACT(H18,"not_issue"),EXACT(H18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(I18,"substantive"),EXACT(I18,"minor_presentation"),EXACT(I18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),J18&lt;&gt;"",NOT(OR(EXACT(J18,"direct"),EXACT(J18,"possible"),EXACT(J18,"unlikely"),EXACT(J18,"unknown")))),AND(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material")),NOT(OR(EXACT(K18,"substantive_inconsistency"),EXACT(K18,"minor_presentation"),EXACT(K18,"non_inconsistency"),EXACT(K18,"indeterminate")))),AND(AND(D18="retain",E18="protocol_report"),L18&lt;&gt;"",NOT(OR(EXACT(L18,"substantive_difference"),EXACT(L18,"minor_presentation"),EXACT(L18,"version_timing"),EXACT(L18,"non_inconsistency"),EXACT(L18,"indeterminate"))))),"CHECK FIELDS",IF(AND(F18&lt;&gt;"",NOT(OR(EXACT(F18,"no"),EXACT(F18,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F18,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J18" s="22">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>IF(AND(OR(D18="retain",D18=""),OR(E18="report_internal_inconsistency",E18="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L18" s="22">
+        <f>IF(AND(OR(D18="retain",D18=""),E18="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M18" s="20" t="n"/>
+      <c r="N18" s="23" t="n"/>
+      <c r="O18" s="23" t="n"/>
+      <c r="P18" s="23" t="n"/>
+      <c r="Q18" s="23" t="n"/>
+      <c r="R18" s="22" t="n"/>
+    </row>
+    <row r="19" ht="92" customHeight="1" s="25">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.11178::C018</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>Physical-function omnibus P values and contrast intervals</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>Results supplement PDF p17, eTable 11 Physical Functioning 6 months — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF p17, eTable 11 Physical Functioning 12 months — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF p17, all other 19 eTable 11 outcome/time rows — joi250046supp4_prod_1755300121.15587.pdf (REPORT, same-display corroboration); Results supplement PDF p18, eTable 11 note b — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Results supplement PDF page 15, Additional Unadjusted Data and Analyses — joi250046supp4_prod_1755300121.15587.pdf (REPORT); Main article PDF p11, Table 3 note c — jama_debar_2025_oi_250046_1755300121.13587.pdf (REPORT, corroboration only); Main article PDF p4, Statistical Analysis — jama_debar_2025_oi_250046_1755300121.13587.pdf (REPORT, corroboration only); The rendered p17 heading is unadjusted between-group mean differences (95%CI), with PT vs UC, HC vs UC and HC vs PT columns and a separately named omnibus P column. No pairwise P value is printed. The comparison does not equate raw medians with fitted means, and does not equate a single pairwise null with the omnibus null</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="n"/>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G19" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A19="",COUNTIF($A$2:$A$19,A19)&lt;&gt;1,LEFT(A19,LEN("2025::jama.2025.11178::"))&lt;&gt;"2025::jama.2025.11178::"),"CHECK KEY",IF(OR(AND(NOT(AND(D19="retain",E19="statistical_results")),H19&lt;&gt;"",NOT(EXACT(H19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),I19&lt;&gt;"",NOT(EXACT(I19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),J19&lt;&gt;"",NOT(EXACT(J19,"not_applicable"))),AND(NOT(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material"))),K19&lt;&gt;"",NOT(EXACT(K19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="protocol_report")),L19&lt;&gt;"",NOT(EXACT(L19,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D19,"retain"),EXACT(D19,"exclude"),EXACT(D19,"discuss"))),NOT(OR(EXACT(E19,"statistical_results"),EXACT(E19,"report_internal_inconsistency"),EXACT(E19,"plan_material"),EXACT(E19,"protocol_report"))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(H19,"confirmed_issue"),EXACT(H19,"probable_issue"),EXACT(H19,"not_issue"),EXACT(H19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(I19,"substantive"),EXACT(I19,"minor_presentation"),EXACT(I19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),J19&lt;&gt;"",NOT(OR(EXACT(J19,"direct"),EXACT(J19,"possible"),EXACT(J19,"unlikely"),EXACT(J19,"unknown")))),AND(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material")),NOT(OR(EXACT(K19,"substantive_inconsistency"),EXACT(K19,"minor_presentation"),EXACT(K19,"non_inconsistency"),EXACT(K19,"indeterminate")))),AND(AND(D19="retain",E19="protocol_report"),L19&lt;&gt;"",NOT(OR(EXACT(L19,"substantive_difference"),EXACT(L19,"minor_presentation"),EXACT(L19,"version_timing"),EXACT(L19,"non_inconsistency"),EXACT(L19,"indeterminate"))))),"CHECK FIELDS",IF(AND(F19&lt;&gt;"",NOT(OR(EXACT(F19,"no"),EXACT(F19,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F19,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J19" s="22">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K19" s="21">
+        <f>IF(AND(OR(D19="retain",D19=""),OR(E19="report_internal_inconsistency",E19="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L19" s="22">
+        <f>IF(AND(OR(D19="retain",D19=""),E19="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+      <c r="R19" s="22" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R19"/>
+  <conditionalFormatting sqref="H2:H19">
+    <cfRule type="expression" priority="8" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I19">
+    <cfRule type="expression" priority="9" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J19">
+    <cfRule type="expression" priority="10" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K19">
+    <cfRule type="expression" priority="11" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L19">
+    <cfRule type="expression" priority="12" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G19">
+    <cfRule type="expression" priority="13" dxfId="71">
+      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"retain,exclude,discuss"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"no,primary_done"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10672,7 +11751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="14" min="1" max="1"/>
@@ -10767,14 +11846,412 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="26" t="inlineStr">
-        <is>
-          <t>Placeholder: no workflow 1.6.2 output for this paper yet; nothing to review in v.2.4.1.</t>
-        </is>
-      </c>
+    <row r="2" ht="92" customHeight="1" s="25">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C001</t>
+        </is>
+      </c>
+      <c r="B2" s="20" t="inlineStr">
+        <is>
+          <t>PROMIS-29 scalar scoring and direction are not specified</t>
+        </is>
+      </c>
+      <c r="C2" s="20" t="inlineStr">
+        <is>
+          <t>jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 3, Secondary Outcomes: domain definition and direction; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Secondary Outcomes: single scalar result; joi250066supp3_prod_1761597796.4701.pdf — p. 15, eTable 4, PROMIS 29 row: corroborating scalar and adjusted result; joi250066supp1_prod_1761597796.4601.pdf — p. 70, PROMIS assessment: contextual scale description</t>
+        </is>
+      </c>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F2" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G2" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$7,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K2" s="21">
+        <f>IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L2" s="22">
+        <f>IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M2" s="20" t="n"/>
+      <c r="N2" s="23" t="n"/>
+      <c r="O2" s="23" t="n"/>
+      <c r="P2" s="23" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="92" customHeight="1" s="25">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C002</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>Primary analysis population changes from all randomized participants to survivors</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 86, §§11.4.1–11.4.2: FAS and primary assignment; joi250066supp1_prod_1761597796.4601.pdf — p. 87, §11.5: missing-data rule; joi250066supp2_prod_1761597796.4701.pdf — p. 4, §3.2 and footnote: deceased participants' contribution; joi250066supp2_prod_1761597796.4701.pdf — p. 6, §4.3: primary/supportive status; joi250066supp2_prod_1761597796.4701.pdf — p. 7, §§4.3.1–4.3.3: primary versus death-inclusive strategy; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, Statistical Analyses: survivor-primary rule; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, flow and SAP explanation: participant totals and timing; joi250066supp3_prod_1761597796.4701.pdf — p. 12, population definitions: primary death exclusion; joi250066supp3_prod_1761597796.4701.pdf — p. 13, eTable 2, estimands 1, 3 and 4: primary and death-inclusive results</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G3" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$7,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K3" s="21">
+        <f>IF(AND(OR(D3="retain",D3=""),OR(E3="report_internal_inconsistency",E3="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L3" s="22">
+        <f>IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M3" s="24" t="n"/>
+      <c r="N3" s="23" t="n"/>
+      <c r="O3" s="23" t="n"/>
+      <c r="P3" s="23" t="n"/>
+      <c r="Q3" s="23" t="n"/>
+      <c r="R3" s="22" t="n"/>
+    </row>
+    <row r="4" ht="92" customHeight="1" s="25">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C003</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>Primary mixed-model terms are absent from the implemented linear model</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 56, statistical synopsis: final mixed-model summary; joi250066supp1_prod_1761597796.4601.pdf — p. 86, §11.4.2: final primary formula/variance structure; joi250066supp2_prod_1761597796.4701.pdf — p. 10, §5.2: baseline/treatment linear model; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, Statistical Analyses: reported model; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, alignment explanation: SAP timing and alignment context; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Primary Outcome: affected primary result; joi250066supp5_prod_1761597796.4751.pdf — p. 1, code lines 19–26 and 31–32: explicit implementation and pooling; joi250066supp1_prod_1761597796.4601.pdf — p. 10, earlier synopsis: historical center-term context; joi250066supp1_prod_1761597796.4601.pdf — p. 39, earlier §11.4.2: historical center-term context</t>
+        </is>
+      </c>
+      <c r="D4" s="21" t="n"/>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F4" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G4" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$7,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K4" s="21">
+        <f>IF(AND(OR(D4="retain",D4=""),OR(E4="report_internal_inconsistency",E4="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L4" s="22">
+        <f>IF(AND(OR(D4="retain",D4=""),E4="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M4" s="20" t="n"/>
+      <c r="N4" s="23" t="n"/>
+      <c r="O4" s="23" t="n"/>
+      <c r="P4" s="23" t="n"/>
+      <c r="Q4" s="23" t="n"/>
+      <c r="R4" s="22" t="n"/>
+    </row>
+    <row r="5" ht="92" customHeight="1" s="25">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C004</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Secondary missing-data procedures differ from the SAP rule</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>joi250066supp2_prod_1761597796.4701.pdf — p. 5, §4.2: secondary-outcome status; joi250066supp2_prod_1761597796.4701.pdf — p. 11, §6: general imputation rule; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, secondary methods: reported nonimputation; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, mRS/PRAI results: affected outcomes; joi250066supp3_prod_1761597796.4701.pdf — p. 7, deviations: mRS death assignment and PRAI exception; joi250066supp3_prod_1761597796.4701.pdf — p. 15, eTable 4: mRS/PRAI results and populations</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="n"/>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G5" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$7,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K5" s="21">
+        <f>IF(AND(OR(D5="retain",D5=""),OR(E5="report_internal_inconsistency",E5="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L5" s="22">
+        <f>IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M5" s="24" t="n"/>
+      <c r="N5" s="23" t="n"/>
+      <c r="O5" s="23" t="n"/>
+      <c r="P5" s="23" t="n"/>
+      <c r="Q5" s="23" t="n"/>
+      <c r="R5" s="22" t="n"/>
+    </row>
+    <row r="6" ht="92" customHeight="1" s="25">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C005</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Planned primary-endpoint supplementary analyses are not identified in the report</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>joi250066supp1_prod_1761597796.4601.pdf — p. 86, §§11.4.1 and 11.4.3: primary sensitivities and bounded PP context; joi250066supp2_prod_1761597796.4701.pdf — p. 11, §7: center interaction model; joi250066supp2_prod_1761597796.4701.pdf — p. 12, §7.2: seven-variable subgroup package; joi250066supp2_prod_1761597796.4701.pdf — p. 15, addendum: subgroup directions and median splits; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 4, supplementary/post hoc estimands: reported analysis and adherence context; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 5, subgroup/center/spline methods: related reported analyses and prespecification statement; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, primary/sensitivity results: affected primary analysis package; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 7, Additional Post Hoc Analyses: baseline analyses; joi250066supp3_prod_1761597796.4701.pdf — p. 1, complete display index: nine eTables and seven eFigures; joi250066supp3_prod_1761597796.4701.pdf — p. 13, eTable 2: eight prespecified estimands; joi250066supp3_prod_1761597796.4701.pdf — p. 14, eTable 3: post hoc estimands; joi250066supp3_prod_1761597796.4701.pdf — p. 18, eTables 7–8: baseline interaction/spline models; joi250066supp3_prod_1761597796.4701.pdf — p. 25, eFigure 5: center graph; joi250066supp3_prod_1761597796.4701.pdf — p. 27, eFigure 7: post hoc forest</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="n"/>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>protocol_report</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G6" s="20">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$7,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K6" s="21">
+        <f>IF(AND(OR(D6="retain",D6=""),OR(E6="report_internal_inconsistency",E6="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L6" s="22">
+        <f>IF(AND(OR(D6="retain",D6=""),E6="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M6" s="20" t="n"/>
+      <c r="N6" s="23" t="n"/>
+      <c r="O6" s="23" t="n"/>
+      <c r="P6" s="23" t="n"/>
+      <c r="Q6" s="23" t="n"/>
+      <c r="R6" s="22" t="n"/>
+    </row>
+    <row r="7" ht="92" customHeight="1" s="25">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>2025::jama.2025.15185::C006</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Serious-event hierarchy counts do not reconcile with their parent totals</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Table 2, levodopa serious-event parent and all 13 top-level category rows; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Table 2, placebo infection parent and all six infection subtype rows; jama_engelter_2025_oi_250066_1761597796.45511.pdf — p. 6, Adverse Events narrative and table notes: corroborating event totals and unit context</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="n"/>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>statistical_results</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G7" s="24">
+        <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$7,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
+        <v/>
+      </c>
+      <c r="H7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="I7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="J7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="statistical_results"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="K7" s="21">
+        <f>IF(AND(OR(D7="retain",D7=""),OR(E7="report_internal_inconsistency",E7="plan_material")),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="L7" s="22">
+        <f>IF(AND(OR(D7="retain",D7=""),E7="protocol_report"),"","not_applicable")</f>
+        <v/>
+      </c>
+      <c r="M7" s="24" t="n"/>
+      <c r="N7" s="23" t="n"/>
+      <c r="O7" s="23" t="n"/>
+      <c r="P7" s="23" t="n"/>
+      <c r="Q7" s="23" t="n"/>
+      <c r="R7" s="22" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R7"/>
+  <conditionalFormatting sqref="H2:H7">
+    <cfRule type="expression" priority="8" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I7">
+    <cfRule type="expression" priority="9" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J7">
+    <cfRule type="expression" priority="10" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="statistical_results"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K7">
+    <cfRule type="expression" priority="11" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),OR($E2="report_internal_inconsistency",$E2="plan_material")))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L7">
+    <cfRule type="expression" priority="12" dxfId="70">
+      <formula>NOT(AND(OR($D2="retain",$D2=""),$E2="protocol_report"))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G7">
+    <cfRule type="expression" priority="13" dxfId="71">
+      <formula>G2&lt;&gt;"PRIMARY READY"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"retain,exclude,discuss"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"statistical_results,report_internal_inconsistency,plan_material,protocol_report"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"no,primary_done"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"confirmed_issue,probable_issue,not_issue,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive,minor_presentation,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"direct,possible,unlikely,unknown,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_inconsistency,minor_presentation,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Use a listed option" error="Choose an option; G also checks pasted entries." type="list" errorStyle="stop">
+      <formula1>"substantive_difference,minor_presentation,version_timing,non_inconsistency,indeterminate,not_applicable"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
+++ b/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\juliz\ai-paper-val\human_adjudication\human_adjudication_v_2_4_1\2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Debian\home\bulun-debian\ai-paper-val\human_adjudication\human_adjudication_v_2_4_1\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EF3B1C6-D32B-4D5B-B7B6-810E41936EB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285DAA0F-5730-4B8B-9779-1FFEF4FFB832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="967" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="967" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="624">
   <si>
     <t>Field</t>
   </si>
@@ -1784,99 +1784,99 @@
   </si>
   <si>
     <t>R_BT</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>BulunTe</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Review1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The abstract's no-significant-difference quality-of-life summary and the body's unqualified no-difference statement do not reconcile with the cited day-7 EQ-5D index P=.02 when read as covering the displayed day-specific contrasts.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The supplied plan specifies a UK hospital-stay difference analysis, while the complete supplied REPORT material presents geometric-mean ratios without the planned additive difference estimate and interval.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Although 'or were not expected to survive beyond 30 days' criteria is not presented in protocol, yet authors have confirmed the limitation in dicusttion 'This may reflect that this study did not include patients unlikely to survive 30 days after the procedure (eg, ASA class 5).'</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>At the same model level, an unstructured covariance allows variances and between-time-point covariances to be freely estimated, whereas an independent structure constrains the between-time-point covariances to zero. This distinction may affect standard errors, confidence intervals, and tests, although the reported text alone does not establish its numerical impact.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SAP §9.6 p.26 lists participant as a fixed effect together with treatment group and baseline score; read literally, these are aliased with participant indicators. The repeated-measures/unstructured-covariance wording makes the intended model clear, so I treat it as a wording slip in the plan.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>RSA C v3.0 (Supp1 p.112) and v6.0 (p.184) list change in muscle strength (HHD and grip) as a secondary efficacy endpoint; R-SAP v1.0/v3.0 (Supp2 pp.76-78, 109-112) and the report (main p.3; Supp3 pp.5-6) treat HHD as exploratory. Outcome-status change; report follows the SAP.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The main article describes plasma NfL analysis as prespecified, whereas Supplement 3 states that it was added post hoc following an assay substitution, "The plasma analysis was pre-specified in Clene Nanomedicine’s Pharmacodynamic SAP originally as UCH-L1 alone, but due to non-availability of the UCH-L1 assay the Neurology 4 Plex-A (including NfL) was analyzed, thus it is considered post-hoc for the purposes of this manuscript"</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Several named planned primary/key-secondary sensitivity, supportive, missingness, follow-up and subgroup analyses have no identifiable quantitative output in the supplied report package.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The latest supplied SAP specifies adjusted primary CAFS rank inference, whereas the report names Wilcoxon rank-sum for its CAFS result, "Revision of Section 6.5.2 CAFS to clarify that the primary CAFS analysis is specified in the ALS Master Protocol Recommended Statistical Analysis, Design and Simulation Report and is an adjusted analysis, to provide code for an adjusted analysis…" in supplement file 2.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Survival methods list five adjustment covariates while the result-table footnote lists the same five plus sex. Inconsistency exists inside main paper, "Rates of death or death-equivalent events (PAV, defined as use of ventilation for &gt;22 hours per day for more than 7 consecutive days) were analyzed using a Cox proportional hazards model, with covariates of prebaseline ALSFRS-R slope, months since symptom onset, riluzole and edaravone use at baseline, and age at baseline." v.s. "Models adjusted for age, sex, time since symptom onset, prebaseline ALSFRS-R slope, riluzole use at baseline, and edaravone use at baseline." in the footnote b of table2.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Missing the result of log-rank tests, which is mentioned in SAP(supp2) as follow "  In the presence of a significant different by the logrank test, inference on whether active treatment extended survival will be based on the hazard ratio estimated from an unadjusted Cox proportional hazards regression.   "</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The article (0.007/0.006) and results supplement (0.010/0.009) give different monthly mortality-component estimates for the matched Bayesian primary model.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The same SVC values are described as 24-week changes and as monthly rates, leaving their quantity and time scale unclear.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Main p.4 says '4 of the 41 participants in the regimen placebo group and 2 in the shared placebo group were excluded' for no follow-up time, but Table 2 (p.7) uses 4/41 as regimen-placebo events and only 2 shared-placebo exclusions (164-2=162). The sentence misattributes the 4 events as exclusions.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Reported prespecified subgroup partitions differ from the supplied prospective delta-FRS and weight definitions.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The protocol's week-24 six-point decline proportion differs from the SAP's first-event decline/death composite.  If a patient died before a 6-point score decrease was documented, the composite endpoint would have occurred  according to the SAP; however, the aforementioned clause in the protocol does not specify how to handle such a   scenario. Therefore, the two definitions cannot be directly considered equivalent, though the SAP may be formally refining the original protocol.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Three NfL table (eTable3) rows give printed confidence-interval and P-value significance readings that do not agree. Maybe caused by rounding issue,</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Clarification is needed regarding whether the changes in serum NfL, between-group differences, and confidence intervals are on the log scale or the back-transformed percentage scale. The current values suggest that the scales may have been mixed, but they are insufficient to determine the underlying derivation process.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The supplied primary-design simulation prose describes decreasing estimated DRR where its table shows an increasing DRR sequence.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>A visible dash before a wrapped decimal permits a signed CAFS probability reading that conflicts with the positive matched-control figure. But since probability could not be negative, this is not an issue.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>For below-quantitation serum NfL values, the SAP specifies LOQ replacement while the results supplement specifies assay LOD replacement (imputation), which might affect results substantilly, since the author said "This result suggests that the magnitude but not directionality of the analysis of serum NfL was sensitive to the effect of an outlier." in the "Biomarker Analyses"</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1892,48 +1892,48 @@
       </rPr>
       <t xml:space="preserve"> However, page 4 of the main text states that "The intention-to-treat principle was used for all analyses"; the primary model estimates efficacy according to randomized groups, and course minutes are not included among the listed model variables. This discrepancy in description does not in itself alter the extracted RR, confidence intervals, or sample size, nor is it sufficient to infer a change in statistical significance.</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> The printed randomized painTRAINER adherence count of 371 (43%) does not reconcile with the randomized denominator of 776.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>C003 concerns the standardized mean differences (SMDs) in Table 3: multiple values cannot be reconciled using the methods stated in the paper, and some even have signs opposite to those of the corresponding mean differences. This   may directly affect downstream meta-analyses that utilize these SMDs; however, at present, it cannot be concluded on this basis that the primary efficacy findings have changed.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>C004 pertains to three integer NNT values that do not strictly correspond to the direct reciprocals of the
   percentages reported in the table. However,rounding up, combined with unshown decimal places, can account for these three values.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Age was actually included in the analytical model and was referred to in the supplementary materials as a "prespecified baseline adjustment variable"; however, age was not listed in the study protocol, the SAP's primary analysis adjustment list, or the main text.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The report explicitly adds the baseline value of each secondary outcome to adjustment, while the plans’ explicit secondary lists name baseline pain severity and stratification variables.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The characterization of the hierarchy between "primary analysis / sensitivity analysis" is not fully consistent between the SAP and the published report. Upon re-examination, the use of imputation and weighting in the primary analysis has an explicit basis in the SAP revisions, and it cannot be concluded that it deviated from the plan solely based on the retained MAR statement.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>In the supplementary materials, the overall P-values for physical function at 6 and 12 months cannot be reconciled with the between-group differences and 95% confidence intervals in the same row under conventional Wald test reconstruction. Currently, there is no evidence to suggest that this would overturn the paper's primary conclusions; its impact on downstream analyses depends on whether these two P-values are utilized.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>C017 concerns the proportion of depression in the supplementary workbook: for the same group, it reports 711 individuals, a total of 1,568, and 2 missing, yet the percentage is labeled as 73.2%. Calculating according to the explicit denominator rule within the table yields approximately 45.4%. This substantially impacts the interpretation of this group's baseline characteristics and differences in loss to follow-up.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The explanation of interval construction is insufficient, making it impossible to reconcile the interpretation of the certainty of benefit for the same comparison.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The explanatory text refers to them as "means," whereas the table title and column headers label them as "medians and quartiles." Consequently, the statistical interpretation of the group values and the parenthetical ranges reported in the table remains ambiguous.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1958,58 +1958,76 @@
       </rPr>
       <t>of 18–38.</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>C015 pertains to the ambiguous sample size definition in supplementary table eTable 8: the first group header labels the participant counts across the three groups as counts "at 3 months," totaling 454, yet it also states that only 366 participants completed at least one follow-up visit. If the former represents participants who actually completed the 3-month follow-up, the two figures cannot be reconciled; if it denotes the randomized sample size, the discrepancy can be explained.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>C010 pertains to multiple instances in Table 3 where SMD point estimates fall outside their corresponding 95% confidence intervals. A total of 14 instances were verified; among them, 9 instances remain irreconcilable even after accounting for reporting precision, while the remaining 5 differ by only 0.01.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>C014 concerns the correspondence between the 95% confidence intervals and P-values across 10 rows in the supplementary materials. In 7 of these rows, the intervals clearly exclude zero yet report P &gt; 0.05, which warrants clarification; in the remaining 3 rows, an interval endpoint is printed exactly as 1, which can likely be explained  simply by rounding</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> The restricted-primary subset analysis attribution and its explicit adjustment footnote differ on education and employment membership from the full selected primary mode</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>The report describes seven differently oriented PROMIS-29 domains but reports one scalar mean and adjusted effect without identifying its aggregation, transformation or direction.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>In Table 2, the sums of the category counts exceed their corresponding totals in two instances.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Protocol §11.4.1-11.4.2 (p.86) and §11.5 (p.87): primary analysis in the FAS of all randomized, missing data by multiple imputation. SAP (p.4 footnote 1; §4.3) and report (main p.4; Supp3 pp.12-13) exclude the 28 participants who died before 3 months from the primary analysis (n=582 of 610); death-inclusive analyses (estimands 3, 4; post hoc estimand 10) are supportive. Report calls the protocol-SAP differences 'terminology' (main p.5).</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Every supplied protocol version specifies a mixed model with a random center intercept (synopses pp.10, 56; §11.4.2 pp.39, 86), and the final version adds stroke type as a fixed effect. SAP §5.2 (p.10), main p.4 and the code (Supp5, OCR: lm(fma_affected.Visit_3 ~ fma_affected.Visit_1.cent + medication)) fit baseline FMA and treatment only. Randomization was minimized within center (main p.3), but center is not in the analysis model.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Not found in any report document (main article; Supp3 index of 9 eTables and 7 eFigures; Supp4 is the investigator list): SAP §7 center and treatment-by-center interaction model, SAP §7.2 seven prespecified subgroup interactions with forest plot (ICEMAN addendum pp.14-15), protocol §11.4.3(b) treatment x stroke type and (c) added-covariable analyses. Planned analyses reported as 'post hoc': center plot (eFigure 5) and the protocol per-protocol set (estimand 11). Main p.5 says prespecified analyses were performed as outlined in the SAP.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>SAP §6 (p.11): missing secondary outcomes imputed as for the primary analysis (100 MICE imputations); only harm outcomes not imputed. Report (main p.5; Supp3 p.7 deviations) did not impute mRS (deaths set to 6; analysis n=596) or the patient-reported relevance item (PRAI; n=546). Disclosed as SAP deviations in Supp3 p.7.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> Continuity-corrected two-proportion power (R) reproduces the other cells within about 2 points (e.g., 41.8/20.5/52.1 vs 41/20/52 in the same row) but gives 28.6% for this cell. Subgroup power is low either way.</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>The criteria for moderate hyperglycemia were not fully consistent across the article, operations manual, and Statistical Analysis Plan (SAP). Although the available evidence confirms discrepancies in the written definitions, it remains unclear how many participants were affected by differential classification and to what extent the reported risk ratio would consequently change.</t>
+  </si>
+  <si>
+    <t>C002 relates to the analysis of BPD (bronchopulmonary dysplasia) severity. Although the prespecified analysis was ordinal, the article presents category-specific ORs for each BPD severity level relative to “no BPD.” Because these analyses address different statistical estimands, the relationship between the reported results and the prespecified analysis remains unclear from the available materials.</t>
+  </si>
+  <si>
+    <t>C003 indicates that, although the primary outcome of “BPD or death” was reported, several explicitly prespecified supplementary analyses were not found in the provided article or supplementary results. Moreover, some subgroup analyses used alternative definitions of the outcome and gestational-age groupings.</t>
+  </si>
+  <si>
+    <t>Protocol Table 2 (Supp1 p.12; OCR and rendered) prints historical-cohort Grade 3 BPD as 20% (31/294); 31/294=10.5%, and 91 (grade 3 or death) - 31 (death) = 60, 60/294=20.4%, categories then sum to 294. A real typo (31 copied from the death row), but it is background data from a prior cohort, not a design element of this trial.</t>
+  </si>
+  <si>
+    <t>GDB MOP Appendix J Table 1 (Supp2 p.152, OCR) gives factor 4 at 0.125 LPM/2.5 kg; 100 x flow/weight = 5. The same row's 4-kg cell (3.125 -&gt; printed 4) is also off by one. Effect on effective FiO2 is 24% vs 25% at 100% O2 (Table 2, p.154), below the 27%/30% decision thresholds, so physiologic BPD classification is unaffected.</t>
+  </si>
+  <si>
+    <t>C006 identifies a discrepancy in the stated confidence-interval method. Although the supplementary materials describe several low-event-count results as using exact 95% confidence intervals, the reported intervals are reproducible as log-Wald approximate intervals.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -2039,10 +2057,6 @@
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2110,11 +2124,8 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
@@ -2122,50 +2133,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="60">
     <dxf>
@@ -3024,7 +3034,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3721,7 +3731,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R14" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="35" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -4176,7 +4186,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R8" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G8">
     <cfRule type="expression" dxfId="31" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -5207,7 +5217,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R20" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G20">
     <cfRule type="expression" dxfId="27" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -5998,7 +6008,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R15" xr:uid="{00000000-0009-0000-0000-00000C000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G15">
     <cfRule type="expression" dxfId="23" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -6741,7 +6751,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R14" xr:uid="{00000000-0009-0000-0000-00000D000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G14">
     <cfRule type="expression" dxfId="19" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -7052,7 +7062,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R5" xr:uid="{00000000-0009-0000-0000-00000E000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G5">
     <cfRule type="expression" dxfId="15" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -7315,7 +7325,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R4" xr:uid="{00000000-0009-0000-0000-00000F000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="11" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -7578,7 +7588,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R4" xr:uid="{00000000-0009-0000-0000-000010000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G4">
     <cfRule type="expression" dxfId="7" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -7937,7 +7947,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R6" xr:uid="{00000000-0009-0000-0000-000011000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="3" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -8769,7 +8779,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8814,7 +8824,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.11178'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2025.15185'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
-        <v>45</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="55.05" customHeight="1">
@@ -8832,7 +8842,7 @@
       </c>
       <c r="B6" s="6">
         <f>B3-B4</f>
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="55.05" customHeight="1">
@@ -8861,7 +8871,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9053,7 +9063,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9378,7 +9388,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R6" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G6">
     <cfRule type="expression" dxfId="59" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -9535,7 +9545,7 @@
         <v>not_applicable</v>
       </c>
       <c r="L2" s="9" t="str">
-        <f t="shared" ref="L2:L17" si="4">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <f t="shared" ref="L2:L16" si="4">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="M2" s="3"/>
@@ -10305,7 +10315,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R17" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G17">
     <cfRule type="expression" dxfId="55" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -10446,15 +10456,15 @@
         <v>PRIMARY READY</v>
       </c>
       <c r="H2" s="8" t="str">
-        <f t="shared" ref="H2:H19" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="H2:H8" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="I2" s="8" t="str">
-        <f t="shared" ref="I2:I19" si="1">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="I2:I8" si="1">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="J2" s="9" t="str">
-        <f t="shared" ref="J2:J19" si="2">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="J2:J8" si="2">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="K2" s="8" t="str">
@@ -10510,7 +10520,7 @@
         <v>not_applicable</v>
       </c>
       <c r="L3" s="9" t="str">
-        <f t="shared" ref="L2:L19" si="4">IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
+        <f t="shared" ref="L3:L19" si="4">IF(AND(OR(D3="retain",D3=""),E3="protocol_report"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="M3" s="1"/>
@@ -11310,7 +11320,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R19" xr:uid="{00000000-0009-0000-0000-000005000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G19">
     <cfRule type="expression" dxfId="51" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -11500,15 +11510,15 @@
         <v>PRIMARY READY</v>
       </c>
       <c r="H3" s="8" t="str">
-        <f t="shared" ref="H2:H7" si="2">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="H3:H6" si="2">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="I3" s="8" t="str">
-        <f t="shared" ref="I2:I7" si="3">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="I3:I6" si="3">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="J3" s="9" t="str">
-        <f t="shared" ref="J2:J7" si="4">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="J3:J6" si="4">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="K3" s="8" t="str">
@@ -11595,11 +11605,11 @@
         <v>71</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G5" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$7,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.15185::"))&lt;&gt;"2025::jama.2025.15185::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>PRIMARY DRAFT</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H5" s="8" t="str">
         <f t="shared" si="2"/>
@@ -11731,7 +11741,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R7" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="47" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -11901,7 +11911,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R2" xr:uid="{00000000-0009-0000-0000-000007000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2">
     <cfRule type="expression" dxfId="43" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>
@@ -12028,16 +12038,18 @@
       <c r="C2" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E2" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$7,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.16450::"))&lt;&gt;"2025::jama.2025.16450::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H2" s="8" t="str">
         <f t="shared" ref="H2:H7" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
@@ -12055,16 +12067,17 @@
         <f t="shared" ref="K2:K7" si="3">IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
-      <c r="L2" s="9" t="str">
-        <f t="shared" ref="L2:L7" si="4">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
-        <v/>
+      <c r="L2" s="9" t="s">
+        <v>526</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
-      <c r="R2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>618</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="91.95" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -12076,16 +12089,18 @@
       <c r="C3" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G3" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$7,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.16450::"))&lt;&gt;"2025::jama.2025.16450::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H3" s="8" t="str">
         <f t="shared" si="0"/>
@@ -12103,16 +12118,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L3" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L3" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="9"/>
+      <c r="R3" s="9" t="s">
+        <v>619</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="91.95" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -12124,16 +12140,18 @@
       <c r="C4" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E4" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$7,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.16450::"))&lt;&gt;"2025::jama.2025.16450::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -12151,16 +12169,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L4" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L4" s="9" t="s">
+        <v>526</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="9"/>
+      <c r="R4" s="9" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="91.95" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -12172,16 +12191,18 @@
       <c r="C5" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>488</v>
+      </c>
       <c r="E5" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G5" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$7,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.16450::"))&lt;&gt;"2025::jama.2025.16450::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H5" s="8" t="str">
         <f t="shared" si="0"/>
@@ -12195,12 +12216,11 @@
         <f t="shared" si="2"/>
         <v>not_applicable</v>
       </c>
-      <c r="K5" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="K5" s="8" t="s">
+        <v>520</v>
       </c>
       <c r="L5" s="9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="L2:L7" si="4">IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="M5" s="1"/>
@@ -12208,7 +12228,9 @@
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="9"/>
+      <c r="R5" s="9" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="91.95" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -12220,16 +12242,18 @@
       <c r="C6" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E6" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$7,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.16450::"))&lt;&gt;"2025::jama.2025.16450::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -12243,9 +12267,8 @@
         <f t="shared" si="2"/>
         <v>not_applicable</v>
       </c>
-      <c r="K6" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="K6" s="8" t="s">
+        <v>526</v>
       </c>
       <c r="L6" s="9" t="str">
         <f t="shared" si="4"/>
@@ -12256,7 +12279,9 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
-      <c r="R6" s="9"/>
+      <c r="R6" s="9" t="s">
+        <v>622</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="91.95" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -12268,28 +12293,27 @@
       <c r="C7" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E7" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G7" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$7,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.16450::"))&lt;&gt;"2025::jama.2025.16450::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H7" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I7" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J7" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>536</v>
       </c>
       <c r="K7" s="8" t="str">
         <f t="shared" si="3"/>
@@ -12304,11 +12328,13 @@
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
-      <c r="R7" s="9"/>
+      <c r="R7" s="9" t="s">
+        <v>623</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R7" xr:uid="{00000000-0009-0000-0000-000008000000}"/>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="G2:G7">
     <cfRule type="expression" dxfId="39" priority="13">
       <formula>G2&lt;&gt;"PRIMARY READY"</formula>

--- a/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
+++ b/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Debian\home\bulun-debian\ai-paper-val\human_adjudication\human_adjudication_v_2_4_1\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285DAA0F-5730-4B8B-9779-1FFEF4FFB832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B834C5-6C0B-4E1D-A8D5-DF7652FE51A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="967" firstSheet="5" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="967" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="644">
   <si>
     <t>Field</t>
   </si>
@@ -2021,6 +2021,66 @@
   </si>
   <si>
     <t>C006 identifies a discrepancy in the stated confidence-interval method. Although the supplementary materials describe several low-event-count results as using exact 95% confidence intervals, the reported intervals are reproducible as log-Wald approximate intervals.</t>
+  </si>
+  <si>
+    <t>Compared with the original protocol, the primary composite endpoint reported in the paper incorporated an additional HbA1c failure criterion. Participants were classified as not having achieved the primary endpoint if their HbA1c was ≥6.5% at either the 6- or 12-month assessment, regardless of whether they had met the prespecified weight-loss or physical-activity target.</t>
+  </si>
+  <si>
+    <t>eTable 16 (Supp2 p.59) MI-pooled risks 32.2% (AI) vs 31.9% (human) imply RD +0.3 points, but RD is printed -1.1 (one-sided bound -11.5). With Rubin's rules and the unadjusted RD model, pooled RD equals the difference of pooled risks.</t>
+  </si>
+  <si>
+    <t>Protocol (Supp1 pp.6, 15; OCR) averages PA over months 6-11 for the weight-plus-PA branch; Supp2 p.13 averages weekly MVPA over all post-baseline visits (max 11; eTable 8b months 1-11). Amendment v1.4 (03-28-2022; Supp1 p.80) says the PA time frame was 'clarified' but the revised window is not printed, so whether the report follows the amended window cannot be determined.</t>
+  </si>
+  <si>
+    <t>eTable 6 footnote (Supp2 p.45) gives site P=.024 and ethnicity P=.018; from the printed counts (p.44) site gives P=.063 (chi-square), .082 (Yates), .070 (Fisher); ethnicity .064 (chi-square, 4 categories), .055 (Fisher), .035-.044 (2 categories). Neither printed P reproduces.</t>
+  </si>
+  <si>
+    <t>Restriction of the HbA1c-reduction branch to baseline HbA1c 5.7-6.4% was made by dated protocol amendment v1.4 (03-28-2022; Supp1 pp.80-81, OCR), and the report (main p.3; Figure 2 footnote c, 130/130) follows the amended protocol. No difference between the report and the operative plan.</t>
+  </si>
+  <si>
+    <t>eTable 1b (Supp2 p.37): versions 11.100.131 and 122.100.407 each show 5 (5%) of the 183 AI participants; 5/183=2.7%. The other seven rows reproduce with N=183 (e.g., 58/183=31.7%-&gt;32; 109/183=59.6%-&gt;60).</t>
+  </si>
+  <si>
+    <t>The primary analysis was changed from the original protocol’s approach of excluding participants who withdrew or lacked 12-month data to an approach that included all randomized participants and classified those with missing 12-month outcome data as not having achieved the primary endpoint. This change affected both the analysis population and the method for handling missing outcome data. The participant counts reported in the paper are internally consistent.</t>
+  </si>
+  <si>
+    <t>Supp2 p.13: weekly MVPA from valid wear periods is summed and divided by the number of available periods (max 11); non-compliant weeks/months get 0 (pp.13, 30, 49). Summing valid periods (zeros add nothing) over all available periods is exactly zero-imputation, so the descriptions are compatible.</t>
+  </si>
+  <si>
+    <t>Protocol §9.4.7-9.4.8 (Supp1 p.38; OCR) analyzes the primary and component end points with (mixed-effects) logistic regression; report uses unadjusted binomial regression for the risk difference (main p.4). Disclosed in the SAP change table (Supp1 p.86); cluster-robust SEs added post hoc (eTables 19a-b).</t>
+  </si>
+  <si>
+    <t>Supp2 p.13 says missing data within valid days were interpolated and that the printed R code was used; in both loops (pp.15-16) ac_imp is computed but activity_stats() and BoutsOfPA() receive the raw vector ac, and the three BoutsOfPA calls are identical (no threshold argument), so threshold-specific bout outputs cannot differ. Since the missing rate is unkown, the potential impact and substantiveness is hard to determine.</t>
+  </si>
+  <si>
+    <t>Protocol §9.4.2/9.4.8 (Supp1 pp.38-39; OCR) plans multiple imputation for PA if &gt;5% missing, with a complete-case sensitivity analysis; report assigns 0 min/week to non-wear periods (worst case; Supp2 pp.13, 30, 49) with best-case sensitivity analyses. Disclosed in the SAP change table (Supp1 p.86).</t>
+  </si>
+  <si>
+    <t>Protocol §5.5.1/Table 1 (Supp1 p.18; OCR) recruitment-pool figures are inconsistent (21,410 vs 21,346 eligible; 13,910/21,346=65.2% printed 56%; 4,892/8,751=55.9% printed 60%), but these are feasibility estimates of portal access, not a design element the analysis relies on.</t>
+  </si>
+  <si>
+    <t>Under the original protocol, the per-protocol analysis was to be conducted in participants who completed the intervention program. In the report, however, the analysis population was redefined as participants with complete 12-month outcome data who had not initiated prohibited medications. The protocol-defined and report-defined populations therefore differed in both their inclusion criteria and sample sizes.</t>
+  </si>
+  <si>
+    <t>It is unclear from the descriptions provided in different sections of the paper whether the Fine–Gray model that yielded the primary endpoint estimate of sHR = 1.02 (95% CI, 0.74–1.39) included study center as a covariate.</t>
+  </si>
+  <si>
+    <t>SAP §3.6 (Supp2 pp.7-9, OCR) and protocol statistical sections plan etiology-adjusted Cox, general linear and Poisson models (with log-rank/Wilcoxon tests) for mortality, ECMO/ventilation/organ failure-free days, ICU/hospital stay and SAE counts; the report gives unadjusted differences with bootstrap CIs and crude RRs (Table 2 footnotes b-c), and no adjusted secondary output.</t>
+  </si>
+  <si>
+    <t>C002 concerns the SOFA component threshold used to define “organ failure/free days.” The SAP specified organ failure as a score &gt;2 in at least one SOFA component, whereas the main article required every component score to be 0 or 1 for a day to qualify as free of organ failure. These definitions differ in how they classify days on which a component score is exactly 2.</t>
+  </si>
+  <si>
+    <t>The protocol specified a post–cardiac arrest subgroup; however, the paper described a broader “Other” subgroup as predefined or prespecified and reported results for that subgroup. No separate results for the post–cardiac arrest subgroup were identified in the materials provided.</t>
+  </si>
+  <si>
+    <t>Protocol (Supp1 pp.14-15 and repeats) and SAP §2.2/§3.6 (Supp2 pp.4, 7-8) plan ECMO-free and ventilation-free days at D30 and D60; main p.3 lists both windows as predefined, but only day-30 values are reported (Table 2 p.6; eTable 3 Supp3 p.5). Searched main and Supp3 for D60 free-day outputs: none. A narrative summary was provided (main paper page 7), but Day 60 (D60) free-day outcomes were not reported in a form that allowed them to be separately identified, extracted, and verified.</t>
+  </si>
+  <si>
+    <t>SAP §2.2/§3.6 (Supp2 pp.4, 7; OCR) define MACE without dialysis; the protocol (Supp1 pp.8, 14-15, all versions) and the report (main p.3; eTable 3 component rows, Supp3 p.5) include dialysis. The report is itself inconsistent: eFigure 4 title (Supp3 p.1/p.10) defines MACE without dialysis.</t>
+  </si>
+  <si>
+    <t>SAP §3.6 (Supp2 p.8, OCR) analyzes left ventricular function at day 30 with a Global Net Benefit hierarchical composite (death, heart transplant, LVEF &gt;30%) with bootstrap CI; the report gives only median LVEF among survivors, 45 vs 40%, difference 5 (-0 to 10) (eTable 3, Supp3 p.5). Protocol lists LVEF at day 30 without the composite.</t>
   </si>
 </sst>
 </file>
@@ -3115,16 +3175,18 @@
       <c r="C2" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E2" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$14,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H2" s="8" t="str">
         <f t="shared" ref="H2:H14" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
@@ -3142,16 +3204,17 @@
         <f t="shared" ref="K2:K14" si="3">IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
-      <c r="L2" s="9" t="str">
-        <f t="shared" ref="L2:L14" si="4">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
-        <v/>
+      <c r="L2" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
-      <c r="R2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>624</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="91.95" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -3163,16 +3226,18 @@
       <c r="C3" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G3" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$14,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H3" s="8" t="str">
         <f t="shared" si="0"/>
@@ -3190,16 +3255,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L3" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L3" s="9" t="s">
+        <v>557</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="9"/>
+      <c r="R3" s="9" t="s">
+        <v>626</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="91.95" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -3211,16 +3277,18 @@
       <c r="C4" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>488</v>
+      </c>
       <c r="E4" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$14,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -3238,16 +3306,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L4" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L4" s="9" t="s">
+        <v>520</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="9"/>
+      <c r="R4" s="9" t="s">
+        <v>628</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="91.95" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -3259,16 +3328,18 @@
       <c r="C5" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>488</v>
+      </c>
       <c r="E5" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G5" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$14,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H5" s="8" t="str">
         <f t="shared" si="0"/>
@@ -3287,15 +3358,17 @@
         <v>not_applicable</v>
       </c>
       <c r="L5" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+        <f t="shared" ref="L2:L14" si="4">IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <v>not_applicable</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="9"/>
+      <c r="R5" s="9" t="s">
+        <v>630</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="91.95" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -3307,16 +3380,18 @@
       <c r="C6" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E6" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$14,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -3334,16 +3409,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L6" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L6" s="9" t="s">
+        <v>526</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
-      <c r="R6" s="9"/>
+      <c r="R6" s="9" t="s">
+        <v>632</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="91.95" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -3355,16 +3431,18 @@
       <c r="C7" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E7" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G7" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$14,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H7" s="8" t="str">
         <f t="shared" si="0"/>
@@ -3382,16 +3460,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L7" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L7" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
-      <c r="R7" s="9"/>
+      <c r="R7" s="9" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="8" spans="1:18" ht="91.95" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -3403,16 +3482,18 @@
       <c r="C8" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E8" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G8" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$14,A8)&lt;&gt;1,LEFT(A8,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -3430,16 +3511,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L8" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L8" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
-      <c r="R8" s="9"/>
+      <c r="R8" s="9" t="s">
+        <v>636</v>
+      </c>
     </row>
     <row r="9" spans="1:18" ht="91.95" customHeight="1">
       <c r="A9" s="1" t="s">
@@ -3451,16 +3533,18 @@
       <c r="C9" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="8" t="s">
+        <v>488</v>
+      </c>
       <c r="E9" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G9" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$14,A9)&lt;&gt;1,LEFT(A9,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H9" s="8" t="str">
         <f t="shared" si="0"/>
@@ -3476,7 +3560,7 @@
       </c>
       <c r="K9" s="8" t="str">
         <f t="shared" si="3"/>
-        <v/>
+        <v>not_applicable</v>
       </c>
       <c r="L9" s="9" t="str">
         <f t="shared" si="4"/>
@@ -3487,7 +3571,9 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
-      <c r="R9" s="9"/>
+      <c r="R9" s="9" t="s">
+        <v>635</v>
+      </c>
     </row>
     <row r="10" spans="1:18" ht="91.95" customHeight="1">
       <c r="A10" s="3" t="s">
@@ -3499,28 +3585,27 @@
       <c r="C10" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E10" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G10" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A10="",COUNTIF($A$2:$A$14,A10)&lt;&gt;1,LEFT(A10,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D10="retain",E10="statistical_results")),H10&lt;&gt;"",NOT(EXACT(H10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),I10&lt;&gt;"",NOT(EXACT(I10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),J10&lt;&gt;"",NOT(EXACT(J10,"not_applicable"))),AND(NOT(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material"))),K10&lt;&gt;"",NOT(EXACT(K10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="protocol_report")),L10&lt;&gt;"",NOT(EXACT(L10,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D10,"retain"),EXACT(D10,"exclude"),EXACT(D10,"discuss"))),NOT(OR(EXACT(E10,"statistical_results"),EXACT(E10,"report_internal_inconsistency"),EXACT(E10,"plan_material"),EXACT(E10,"protocol_report"))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(H10,"confirmed_issue"),EXACT(H10,"probable_issue"),EXACT(H10,"not_issue"),EXACT(H10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(I10,"substantive"),EXACT(I10,"minor_presentation"),EXACT(I10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),J10&lt;&gt;"",NOT(OR(EXACT(J10,"direct"),EXACT(J10,"possible"),EXACT(J10,"unlikely"),EXACT(J10,"unknown")))),AND(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material")),NOT(OR(EXACT(K10,"substantive_inconsistency"),EXACT(K10,"minor_presentation"),EXACT(K10,"non_inconsistency"),EXACT(K10,"indeterminate")))),AND(AND(D10="retain",E10="protocol_report"),L10&lt;&gt;"",NOT(OR(EXACT(L10,"substantive_difference"),EXACT(L10,"minor_presentation"),EXACT(L10,"version_timing"),EXACT(L10,"non_inconsistency"),EXACT(L10,"indeterminate"))))),"CHECK FIELDS",IF(AND(F10&lt;&gt;"",NOT(OR(EXACT(F10,"no"),EXACT(F10,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F10,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H10" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I10" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J10" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="K10" s="8" t="str">
         <f t="shared" si="3"/>
@@ -3535,7 +3620,9 @@
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
-      <c r="R10" s="9"/>
+      <c r="R10" s="9" t="s">
+        <v>633</v>
+      </c>
     </row>
     <row r="11" spans="1:18" ht="91.95" customHeight="1">
       <c r="A11" s="1" t="s">
@@ -3547,28 +3634,30 @@
       <c r="C11" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="D11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>488</v>
+      </c>
       <c r="E11" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G11" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A11="",COUNTIF($A$2:$A$14,A11)&lt;&gt;1,LEFT(A11,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D11="retain",E11="statistical_results")),H11&lt;&gt;"",NOT(EXACT(H11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),I11&lt;&gt;"",NOT(EXACT(I11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),J11&lt;&gt;"",NOT(EXACT(J11,"not_applicable"))),AND(NOT(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material"))),K11&lt;&gt;"",NOT(EXACT(K11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="protocol_report")),L11&lt;&gt;"",NOT(EXACT(L11,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D11,"retain"),EXACT(D11,"exclude"),EXACT(D11,"discuss"))),NOT(OR(EXACT(E11,"statistical_results"),EXACT(E11,"report_internal_inconsistency"),EXACT(E11,"plan_material"),EXACT(E11,"protocol_report"))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(H11,"confirmed_issue"),EXACT(H11,"probable_issue"),EXACT(H11,"not_issue"),EXACT(H11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(I11,"substantive"),EXACT(I11,"minor_presentation"),EXACT(I11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),J11&lt;&gt;"",NOT(OR(EXACT(J11,"direct"),EXACT(J11,"possible"),EXACT(J11,"unlikely"),EXACT(J11,"unknown")))),AND(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material")),NOT(OR(EXACT(K11,"substantive_inconsistency"),EXACT(K11,"minor_presentation"),EXACT(K11,"non_inconsistency"),EXACT(K11,"indeterminate")))),AND(AND(D11="retain",E11="protocol_report"),L11&lt;&gt;"",NOT(OR(EXACT(L11,"substantive_difference"),EXACT(L11,"minor_presentation"),EXACT(L11,"version_timing"),EXACT(L11,"non_inconsistency"),EXACT(L11,"indeterminate"))))),"CHECK FIELDS",IF(AND(F11&lt;&gt;"",NOT(OR(EXACT(F11,"no"),EXACT(F11,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F11,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H11" s="8" t="str">
         <f t="shared" si="0"/>
-        <v/>
+        <v>not_applicable</v>
       </c>
       <c r="I11" s="8" t="str">
         <f t="shared" si="1"/>
-        <v/>
+        <v>not_applicable</v>
       </c>
       <c r="J11" s="9" t="str">
         <f t="shared" si="2"/>
-        <v/>
+        <v>not_applicable</v>
       </c>
       <c r="K11" s="8" t="str">
         <f t="shared" si="3"/>
@@ -3583,7 +3672,9 @@
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
-      <c r="R11" s="9"/>
+      <c r="R11" s="9" t="s">
+        <v>631</v>
+      </c>
     </row>
     <row r="12" spans="1:18" ht="91.95" customHeight="1">
       <c r="A12" s="3" t="s">
@@ -3595,28 +3686,27 @@
       <c r="C12" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="D12" s="8"/>
+      <c r="D12" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E12" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G12" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A12="",COUNTIF($A$2:$A$14,A12)&lt;&gt;1,LEFT(A12,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D12="retain",E12="statistical_results")),H12&lt;&gt;"",NOT(EXACT(H12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),I12&lt;&gt;"",NOT(EXACT(I12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="statistical_results")),J12&lt;&gt;"",NOT(EXACT(J12,"not_applicable"))),AND(NOT(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material"))),K12&lt;&gt;"",NOT(EXACT(K12,"not_applicable"))),AND(NOT(AND(D12="retain",E12="protocol_report")),L12&lt;&gt;"",NOT(EXACT(L12,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D12,"retain"),EXACT(D12,"exclude"),EXACT(D12,"discuss"))),NOT(OR(EXACT(E12,"statistical_results"),EXACT(E12,"report_internal_inconsistency"),EXACT(E12,"plan_material"),EXACT(E12,"protocol_report"))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(H12,"confirmed_issue"),EXACT(H12,"probable_issue"),EXACT(H12,"not_issue"),EXACT(H12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),NOT(OR(EXACT(I12,"substantive"),EXACT(I12,"minor_presentation"),EXACT(I12,"indeterminate")))),AND(AND(D12="retain",E12="statistical_results"),J12&lt;&gt;"",NOT(OR(EXACT(J12,"direct"),EXACT(J12,"possible"),EXACT(J12,"unlikely"),EXACT(J12,"unknown")))),AND(AND(D12="retain",OR(E12="report_internal_inconsistency",E12="plan_material")),NOT(OR(EXACT(K12,"substantive_inconsistency"),EXACT(K12,"minor_presentation"),EXACT(K12,"non_inconsistency"),EXACT(K12,"indeterminate")))),AND(AND(D12="retain",E12="protocol_report"),L12&lt;&gt;"",NOT(OR(EXACT(L12,"substantive_difference"),EXACT(L12,"minor_presentation"),EXACT(L12,"version_timing"),EXACT(L12,"non_inconsistency"),EXACT(L12,"indeterminate"))))),"CHECK FIELDS",IF(AND(F12&lt;&gt;"",NOT(OR(EXACT(F12,"no"),EXACT(F12,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F12,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H12" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I12" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J12" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>536</v>
       </c>
       <c r="K12" s="8" t="str">
         <f t="shared" si="3"/>
@@ -3631,7 +3721,9 @@
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
-      <c r="R12" s="9"/>
+      <c r="R12" s="9" t="s">
+        <v>629</v>
+      </c>
     </row>
     <row r="13" spans="1:18" ht="91.95" customHeight="1">
       <c r="A13" s="1" t="s">
@@ -3643,28 +3735,27 @@
       <c r="C13" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="D13" s="8"/>
+      <c r="D13" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E13" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G13" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A13="",COUNTIF($A$2:$A$14,A13)&lt;&gt;1,LEFT(A13,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D13="retain",E13="statistical_results")),H13&lt;&gt;"",NOT(EXACT(H13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),I13&lt;&gt;"",NOT(EXACT(I13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="statistical_results")),J13&lt;&gt;"",NOT(EXACT(J13,"not_applicable"))),AND(NOT(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material"))),K13&lt;&gt;"",NOT(EXACT(K13,"not_applicable"))),AND(NOT(AND(D13="retain",E13="protocol_report")),L13&lt;&gt;"",NOT(EXACT(L13,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D13,"retain"),EXACT(D13,"exclude"),EXACT(D13,"discuss"))),NOT(OR(EXACT(E13,"statistical_results"),EXACT(E13,"report_internal_inconsistency"),EXACT(E13,"plan_material"),EXACT(E13,"protocol_report"))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(H13,"confirmed_issue"),EXACT(H13,"probable_issue"),EXACT(H13,"not_issue"),EXACT(H13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),NOT(OR(EXACT(I13,"substantive"),EXACT(I13,"minor_presentation"),EXACT(I13,"indeterminate")))),AND(AND(D13="retain",E13="statistical_results"),J13&lt;&gt;"",NOT(OR(EXACT(J13,"direct"),EXACT(J13,"possible"),EXACT(J13,"unlikely"),EXACT(J13,"unknown")))),AND(AND(D13="retain",OR(E13="report_internal_inconsistency",E13="plan_material")),NOT(OR(EXACT(K13,"substantive_inconsistency"),EXACT(K13,"minor_presentation"),EXACT(K13,"non_inconsistency"),EXACT(K13,"indeterminate")))),AND(AND(D13="retain",E13="protocol_report"),L13&lt;&gt;"",NOT(OR(EXACT(L13,"substantive_difference"),EXACT(L13,"minor_presentation"),EXACT(L13,"version_timing"),EXACT(L13,"non_inconsistency"),EXACT(L13,"indeterminate"))))),"CHECK FIELDS",IF(AND(F13&lt;&gt;"",NOT(OR(EXACT(F13,"no"),EXACT(F13,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F13,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H13" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I13" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J13" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="K13" s="8" t="str">
         <f t="shared" si="3"/>
@@ -3679,7 +3770,9 @@
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
-      <c r="R13" s="9"/>
+      <c r="R13" s="9" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="91.95" customHeight="1">
       <c r="A14" s="3" t="s">
@@ -3691,28 +3784,27 @@
       <c r="C14" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D14" s="8"/>
+      <c r="D14" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E14" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G14" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A14="",COUNTIF($A$2:$A$14,A14)&lt;&gt;1,LEFT(A14,LEN("2025::jama.2025.19563::"))&lt;&gt;"2025::jama.2025.19563::"),"CHECK KEY",IF(OR(AND(NOT(AND(D14="retain",E14="statistical_results")),H14&lt;&gt;"",NOT(EXACT(H14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),I14&lt;&gt;"",NOT(EXACT(I14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="statistical_results")),J14&lt;&gt;"",NOT(EXACT(J14,"not_applicable"))),AND(NOT(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material"))),K14&lt;&gt;"",NOT(EXACT(K14,"not_applicable"))),AND(NOT(AND(D14="retain",E14="protocol_report")),L14&lt;&gt;"",NOT(EXACT(L14,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D14,"retain"),EXACT(D14,"exclude"),EXACT(D14,"discuss"))),NOT(OR(EXACT(E14,"statistical_results"),EXACT(E14,"report_internal_inconsistency"),EXACT(E14,"plan_material"),EXACT(E14,"protocol_report"))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(H14,"confirmed_issue"),EXACT(H14,"probable_issue"),EXACT(H14,"not_issue"),EXACT(H14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),NOT(OR(EXACT(I14,"substantive"),EXACT(I14,"minor_presentation"),EXACT(I14,"indeterminate")))),AND(AND(D14="retain",E14="statistical_results"),J14&lt;&gt;"",NOT(OR(EXACT(J14,"direct"),EXACT(J14,"possible"),EXACT(J14,"unlikely"),EXACT(J14,"unknown")))),AND(AND(D14="retain",OR(E14="report_internal_inconsistency",E14="plan_material")),NOT(OR(EXACT(K14,"substantive_inconsistency"),EXACT(K14,"minor_presentation"),EXACT(K14,"non_inconsistency"),EXACT(K14,"indeterminate")))),AND(AND(D14="retain",E14="protocol_report"),L14&lt;&gt;"",NOT(OR(EXACT(L14,"substantive_difference"),EXACT(L14,"minor_presentation"),EXACT(L14,"version_timing"),EXACT(L14,"non_inconsistency"),EXACT(L14,"indeterminate"))))),"CHECK FIELDS",IF(AND(F14&lt;&gt;"",NOT(OR(EXACT(F14,"no"),EXACT(F14,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F14,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H14" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I14" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J14" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="K14" s="8" t="str">
         <f t="shared" si="3"/>
@@ -3727,7 +3819,9 @@
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
-      <c r="R14" s="9"/>
+      <c r="R14" s="9" t="s">
+        <v>625</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R14" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
@@ -3858,35 +3952,34 @@
       <c r="C2" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E2" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$8,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.19843::"))&lt;&gt;"2025::jama.2025.19843::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H2" s="8" t="str">
-        <f t="shared" ref="H2:H8" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="I2" s="8" t="str">
-        <f t="shared" ref="I2:I8" si="1">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
-      </c>
-      <c r="J2" s="9" t="str">
-        <f t="shared" ref="J2:J8" si="2">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="K2" s="8" t="str">
-        <f t="shared" ref="K2:K8" si="3">IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
+        <f t="shared" ref="K2:K8" si="0">IF(AND(OR(D2="retain",D2=""),OR(E2="report_internal_inconsistency",E2="plan_material")),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="L2" s="9" t="str">
-        <f t="shared" ref="L2:L8" si="4">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <f t="shared" ref="L2:L8" si="1">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="M2" s="3"/>
@@ -3894,7 +3987,9 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
-      <c r="R2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="91.95" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -3906,43 +4001,46 @@
       <c r="C3" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G3" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$8,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.19843::"))&lt;&gt;"2025::jama.2025.19843::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H3" s="8" t="str">
+        <f t="shared" ref="H2:H8" si="2">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v>not_applicable</v>
+      </c>
+      <c r="I3" s="8" t="str">
+        <f t="shared" ref="I2:I8" si="3">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v>not_applicable</v>
+      </c>
+      <c r="J3" s="9" t="str">
+        <f t="shared" ref="J2:J8" si="4">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <v>not_applicable</v>
+      </c>
+      <c r="K3" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not_applicable</v>
       </c>
-      <c r="I3" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="J3" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="K3" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="L3" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L3" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="9"/>
+      <c r="R3" s="9" t="s">
+        <v>639</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="91.95" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -3954,43 +4052,46 @@
       <c r="C4" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E4" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$8,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.19843::"))&lt;&gt;"2025::jama.2025.19843::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H4" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="I4" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="J4" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="K4" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not_applicable</v>
       </c>
-      <c r="I4" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="J4" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="K4" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="L4" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L4" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="9"/>
+      <c r="R4" s="9" t="s">
+        <v>641</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="91.95" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -4002,43 +4103,45 @@
       <c r="C5" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E5" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G5" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$8,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.19843::"))&lt;&gt;"2025::jama.2025.19843::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H5" s="8" t="str">
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="I5" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="J5" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="K5" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not_applicable</v>
       </c>
-      <c r="I5" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="J5" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="K5" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="L5" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L5" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="9"/>
+      <c r="R5" s="9" t="s">
+        <v>643</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="91.95" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -4050,43 +4153,46 @@
       <c r="C6" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E6" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$8,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.19843::"))&lt;&gt;"2025::jama.2025.19843::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H6" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="I6" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="J6" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="K6" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not_applicable</v>
       </c>
-      <c r="I6" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="J6" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="K6" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="L6" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L6" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
-      <c r="R6" s="9"/>
+      <c r="R6" s="9" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="91.95" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -4098,43 +4204,46 @@
       <c r="C7" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D7" s="8"/>
+      <c r="D7" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E7" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G7" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A7="",COUNTIF($A$2:$A$8,A7)&lt;&gt;1,LEFT(A7,LEN("2025::jama.2025.19843::"))&lt;&gt;"2025::jama.2025.19843::"),"CHECK KEY",IF(OR(AND(NOT(AND(D7="retain",E7="statistical_results")),H7&lt;&gt;"",NOT(EXACT(H7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),I7&lt;&gt;"",NOT(EXACT(I7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="statistical_results")),J7&lt;&gt;"",NOT(EXACT(J7,"not_applicable"))),AND(NOT(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material"))),K7&lt;&gt;"",NOT(EXACT(K7,"not_applicable"))),AND(NOT(AND(D7="retain",E7="protocol_report")),L7&lt;&gt;"",NOT(EXACT(L7,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D7,"retain"),EXACT(D7,"exclude"),EXACT(D7,"discuss"))),NOT(OR(EXACT(E7,"statistical_results"),EXACT(E7,"report_internal_inconsistency"),EXACT(E7,"plan_material"),EXACT(E7,"protocol_report"))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(H7,"confirmed_issue"),EXACT(H7,"probable_issue"),EXACT(H7,"not_issue"),EXACT(H7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),NOT(OR(EXACT(I7,"substantive"),EXACT(I7,"minor_presentation"),EXACT(I7,"indeterminate")))),AND(AND(D7="retain",E7="statistical_results"),J7&lt;&gt;"",NOT(OR(EXACT(J7,"direct"),EXACT(J7,"possible"),EXACT(J7,"unlikely"),EXACT(J7,"unknown")))),AND(AND(D7="retain",OR(E7="report_internal_inconsistency",E7="plan_material")),NOT(OR(EXACT(K7,"substantive_inconsistency"),EXACT(K7,"minor_presentation"),EXACT(K7,"non_inconsistency"),EXACT(K7,"indeterminate")))),AND(AND(D7="retain",E7="protocol_report"),L7&lt;&gt;"",NOT(OR(EXACT(L7,"substantive_difference"),EXACT(L7,"minor_presentation"),EXACT(L7,"version_timing"),EXACT(L7,"non_inconsistency"),EXACT(L7,"indeterminate"))))),"CHECK FIELDS",IF(AND(F7&lt;&gt;"",NOT(OR(EXACT(F7,"no"),EXACT(F7,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F7,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H7" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="I7" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="J7" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="K7" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not_applicable</v>
       </c>
-      <c r="I7" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="J7" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="K7" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="L7" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L7" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
-      <c r="R7" s="9"/>
+      <c r="R7" s="9" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="8" spans="1:18" ht="91.95" customHeight="1">
       <c r="A8" s="3" t="s">
@@ -4146,43 +4255,46 @@
       <c r="C8" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E8" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G8" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$8,A8)&lt;&gt;1,LEFT(A8,LEN("2025::jama.2025.19843::"))&lt;&gt;"2025::jama.2025.19843::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H8" s="8" t="str">
+        <f t="shared" si="2"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="I8" s="8" t="str">
+        <f t="shared" si="3"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="J8" s="9" t="str">
+        <f t="shared" si="4"/>
+        <v>not_applicable</v>
+      </c>
+      <c r="K8" s="8" t="str">
         <f t="shared" si="0"/>
         <v>not_applicable</v>
       </c>
-      <c r="I8" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="J8" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="K8" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v>not_applicable</v>
-      </c>
-      <c r="L8" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L8" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
-      <c r="R8" s="9"/>
+      <c r="R8" s="9" t="s">
+        <v>638</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R8" xr:uid="{00000000-0009-0000-0000-00000A000000}"/>
@@ -8824,7 +8936,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.11178'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2025.15185'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="55.05" customHeight="1">
@@ -8842,7 +8954,7 @@
       </c>
       <c r="B6" s="6">
         <f>B3-B4</f>
-        <v>81</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="55.05" customHeight="1">
@@ -12052,15 +12164,15 @@
         <v>PRIMARY READY</v>
       </c>
       <c r="H2" s="8" t="str">
-        <f t="shared" ref="H2:H7" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="H2:H6" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="I2" s="8" t="str">
-        <f t="shared" ref="I2:I7" si="1">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="I2:I6" si="1">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="J2" s="9" t="str">
-        <f t="shared" ref="J2:J7" si="2">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="J2:J6" si="2">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="K2" s="8" t="str">
@@ -12220,7 +12332,7 @@
         <v>520</v>
       </c>
       <c r="L5" s="9" t="str">
-        <f t="shared" ref="L2:L7" si="4">IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <f t="shared" ref="L5:L7" si="4">IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="M5" s="1"/>

--- a/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
+++ b/human_adjudication/human_adjudication_v_2_4_1/2025/human_adjudication_v_2_4_1_2025_R_B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Debian\home\bulun-debian\ai-paper-val\human_adjudication\human_adjudication_v_2_4_1\2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B834C5-6C0B-4E1D-A8D5-DF7652FE51A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBD5782D-5E8E-448E-8770-ACDB4C786168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="967" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="967" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Setup" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1413" uniqueCount="657">
   <si>
     <t>Field</t>
   </si>
@@ -2081,6 +2081,45 @@
   </si>
   <si>
     <t>SAP §3.6 (Supp2 p.8, OCR) analyzes left ventricular function at day 30 with a Global Net Benefit hierarchical composite (death, heart transplant, LVEF &gt;30%) with bootstrap CI; the report gives only median LVEF among survivors, 45 vs 40%, difference 5 (-0 to 10) (eTable 3, Supp3 p.5). Protocol lists LVEF at day 30 without the composite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Report (main pp.1, 3): 134 messages = 100 in month 1 (3-4/day), 30 in month 2 (1/day), then 1/month for 4 months. Protocol v6.0 (Supp1 p.53, OCR) states 134 messages but a schedule of 4-5/day for 2 months, 1-2/day for 2 months and 1/week for 2 months (implying well over 300); v4.0 (p.16) states 178 with a similar schedule. The SAP (p.80) matches the report. </t>
+  </si>
+  <si>
+    <t>SAP §'Adjusted analyses' (Supp1 p.92, OCR) plans a fully adjusted model including tobacco use form with education, smoking duration and other baseline characteristics; the report's adjusted RR 3.2 (2.2-5.2) uses covariates 'selected post hoc' (age, sex, education, occupation, smoking duration), without tobacco form (main pp.3-4, Table 2 note a). Disclosed as post hoc.</t>
+  </si>
+  <si>
+    <t>eTable 9 (Supp2 p.13) treatment failure 0.1% vs 0.6% with absolute difference +0.5 (-0.4 to 1.3); mHealth minus usual care is -0.5. Same sign reversal in main Table 2 (p.6) for death (3.5 vs 7.5; printed +4, 1.0 to 7.1) and treatment failure (0.1 vs 0.5; printed +0.4), whereas other rows are mHealth minus usual care.</t>
+  </si>
+  <si>
+    <t>Protocol v6.0 §21.3-21.4 (Supp1 p.49, rendered) includes people who smoke daily OR stopped/reduced since TB diagnosis, excludes retreatment TB and current tobacco pharmacotherapy; report (main p.2) requires daily smoking (&gt;=1 puff on &gt;=25 days last month), omits retreatment, and Figure 1 (p.4) excludes 236 who 'cannot read and no one in home can read SMS', a criterion not in the plan list.</t>
+  </si>
+  <si>
+    <t>Planned primary outcome uses CO &lt;10 ppm (SAP p.84); the CO &lt;6 ppm analysis is described as post hoc sensitivity (main p.3) but its ITT and PP rows sit under the 'Primary outcome' heading of Table 2 (p.6). Labeling issue; the text makes the status clear.</t>
+  </si>
+  <si>
+    <t>eTable 6 (Supp2 p.9): control site 2008 deaths 5 (7.5%); with 40 recruited per cluster (eTable 5 p.8), 5/40 = 12.5%. The count is right: control-site deaths sum to 27 and mHealth to 25, matching Figure 1.</t>
+  </si>
+  <si>
+    <t>Report (main p.3): quit date set 5 days after enrollment, and continuous abstinence is counted from it. The supplied SMS schedule (Supp1 pp.101-103, OCR) sets the quit date 7 days after day 2 (Q(-8) at Tx(+1), i.e., about day 9) and promises 'up to 5' messages/day. The 5-day quit date appears in the protocol only for the Phase 4 face-to-face arm.</t>
+  </si>
+  <si>
+    <t>Protocol v6.0/v4.0 §28.2.2/§11.2.2 (Supp1 pp.66, 28; OCR) plan primary analysis 'in a missing-at-random architecture'; the SAP (p.91) and report (main p.3) treat missing primary outcomes as not abstinent (Russell Standard), with complete-case analysis as sensitivity.</t>
+  </si>
+  <si>
+    <t>Plan (protocol pp.8, 47; SAP p.84; OCR): cotinine by Accutest NicAlert strips, level &lt;3 (100-200 ng/mL) = abstinent. Report (main p.3): a rapid test cassette (AllTest) with 'a negative result' = abstinent; no cutoff given. Device differs and the equivalence of thresholds cannot be checked.</t>
+  </si>
+  <si>
+    <t>eTable 4 (Supp2 p.6), usual care column: drug user 1 (7.4%) and severe pneumonia 1 (7.4%); 1/27 = 3.7%. Also small rounding slips: 16/27 = 59.3% (printed 59.2), 8/52 = 15.4% (15.2), 3/52 = 5.8% (5.7).</t>
+  </si>
+  <si>
+    <t>Protocol v6.0 §28.2.2 (Supp1 p.66; v4.0 p.28; OCR) plans GLMMs with log link and Poisson distribution to estimate RRs; the report (main p.3) uses mixed-effects logistic regression, as does the SAP (p.91-92). Report follows the SAP, not the protocol.</t>
+  </si>
+  <si>
+    <t>SAP subgroup analyses (Supp1 pp.92-93, OCR) include gender (male vs female); the report's prespecified subgroup list (main p.3) and eTable 8 (Supp2 p.12) omit sex and add an ability-to-read-SMS subgroup. No reason given (only 37 women enrolled).</t>
+  </si>
+  <si>
+    <t>Protocol v6.0 Phase 3 sample-size section (Supp1 p.63; OCR) randomizes 27 clusters 18:9, but the power paragraph (p.65) and overview (p.48) still describe 90% power for 16 clusters vs 8 (the v4.0 allocation; change log p.77 records 16/8 -&gt; 18/9).</t>
   </si>
 </sst>
 </file>
@@ -3189,15 +3228,15 @@
         <v>PRIMARY READY</v>
       </c>
       <c r="H2" s="8" t="str">
-        <f t="shared" ref="H2:H14" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="H2:H11" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="I2" s="8" t="str">
-        <f t="shared" ref="I2:I14" si="1">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="I2:I11" si="1">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="J2" s="9" t="str">
-        <f t="shared" ref="J2:J14" si="2">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="J2:J11" si="2">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="K2" s="8" t="str">
@@ -3358,7 +3397,7 @@
         <v>not_applicable</v>
       </c>
       <c r="L5" s="9" t="str">
-        <f t="shared" ref="L2:L14" si="4">IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
+        <f t="shared" ref="L5:L14" si="4">IF(AND(OR(D5="retain",D5=""),E5="protocol_report"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="M5" s="1"/>
@@ -3979,7 +4018,7 @@
         <v>not_applicable</v>
       </c>
       <c r="L2" s="9" t="str">
-        <f t="shared" ref="L2:L8" si="1">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
+        <f t="shared" ref="L2" si="1">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="M2" s="3"/>
@@ -4015,15 +4054,15 @@
         <v>PRIMARY READY</v>
       </c>
       <c r="H3" s="8" t="str">
-        <f t="shared" ref="H2:H8" si="2">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="H3:H8" si="2">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="I3" s="8" t="str">
-        <f t="shared" ref="I2:I8" si="3">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="I3:I8" si="3">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="J3" s="9" t="str">
-        <f t="shared" ref="J2:J8" si="4">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
+        <f t="shared" ref="J3:J8" si="4">IF(AND(OR(D3="retain",D3=""),E3="statistical_results"),"","not_applicable")</f>
         <v>not_applicable</v>
       </c>
       <c r="K3" s="8" t="str">
@@ -4425,16 +4464,18 @@
       <c r="C2" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="8"/>
+      <c r="D2" s="8" t="s">
+        <v>488</v>
+      </c>
       <c r="E2" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A2="",COUNTIF($A$2:$A$20,A2)&lt;&gt;1,LEFT(A2,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D2="retain",E2="statistical_results")),H2&lt;&gt;"",NOT(EXACT(H2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),I2&lt;&gt;"",NOT(EXACT(I2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="statistical_results")),J2&lt;&gt;"",NOT(EXACT(J2,"not_applicable"))),AND(NOT(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material"))),K2&lt;&gt;"",NOT(EXACT(K2,"not_applicable"))),AND(NOT(AND(D2="retain",E2="protocol_report")),L2&lt;&gt;"",NOT(EXACT(L2,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D2,"retain"),EXACT(D2,"exclude"),EXACT(D2,"discuss"))),NOT(OR(EXACT(E2,"statistical_results"),EXACT(E2,"report_internal_inconsistency"),EXACT(E2,"plan_material"),EXACT(E2,"protocol_report"))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(H2,"confirmed_issue"),EXACT(H2,"probable_issue"),EXACT(H2,"not_issue"),EXACT(H2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),NOT(OR(EXACT(I2,"substantive"),EXACT(I2,"minor_presentation"),EXACT(I2,"indeterminate")))),AND(AND(D2="retain",E2="statistical_results"),J2&lt;&gt;"",NOT(OR(EXACT(J2,"direct"),EXACT(J2,"possible"),EXACT(J2,"unlikely"),EXACT(J2,"unknown")))),AND(AND(D2="retain",OR(E2="report_internal_inconsistency",E2="plan_material")),NOT(OR(EXACT(K2,"substantive_inconsistency"),EXACT(K2,"minor_presentation"),EXACT(K2,"non_inconsistency"),EXACT(K2,"indeterminate")))),AND(AND(D2="retain",E2="protocol_report"),L2&lt;&gt;"",NOT(OR(EXACT(L2,"substantive_difference"),EXACT(L2,"minor_presentation"),EXACT(L2,"version_timing"),EXACT(L2,"non_inconsistency"),EXACT(L2,"indeterminate"))))),"CHECK FIELDS",IF(AND(F2&lt;&gt;"",NOT(OR(EXACT(F2,"no"),EXACT(F2,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F2,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H2" s="8" t="str">
         <f t="shared" ref="H2:H20" si="0">IF(AND(OR(D2="retain",D2=""),E2="statistical_results"),"","not_applicable")</f>
@@ -4454,14 +4495,16 @@
       </c>
       <c r="L2" s="9" t="str">
         <f t="shared" ref="L2:L20" si="4">IF(AND(OR(D2="retain",D2=""),E2="protocol_report"),"","not_applicable")</f>
-        <v/>
+        <v>not_applicable</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
-      <c r="R2" s="9"/>
+      <c r="R2" s="9" t="s">
+        <v>644</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="91.95" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4473,16 +4516,18 @@
       <c r="C3" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="D3" s="8"/>
+      <c r="D3" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E3" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G3" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A3="",COUNTIF($A$2:$A$20,A3)&lt;&gt;1,LEFT(A3,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D3="retain",E3="statistical_results")),H3&lt;&gt;"",NOT(EXACT(H3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),I3&lt;&gt;"",NOT(EXACT(I3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="statistical_results")),J3&lt;&gt;"",NOT(EXACT(J3,"not_applicable"))),AND(NOT(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material"))),K3&lt;&gt;"",NOT(EXACT(K3,"not_applicable"))),AND(NOT(AND(D3="retain",E3="protocol_report")),L3&lt;&gt;"",NOT(EXACT(L3,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D3,"retain"),EXACT(D3,"exclude"),EXACT(D3,"discuss"))),NOT(OR(EXACT(E3,"statistical_results"),EXACT(E3,"report_internal_inconsistency"),EXACT(E3,"plan_material"),EXACT(E3,"protocol_report"))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(H3,"confirmed_issue"),EXACT(H3,"probable_issue"),EXACT(H3,"not_issue"),EXACT(H3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),NOT(OR(EXACT(I3,"substantive"),EXACT(I3,"minor_presentation"),EXACT(I3,"indeterminate")))),AND(AND(D3="retain",E3="statistical_results"),J3&lt;&gt;"",NOT(OR(EXACT(J3,"direct"),EXACT(J3,"possible"),EXACT(J3,"unlikely"),EXACT(J3,"unknown")))),AND(AND(D3="retain",OR(E3="report_internal_inconsistency",E3="plan_material")),NOT(OR(EXACT(K3,"substantive_inconsistency"),EXACT(K3,"minor_presentation"),EXACT(K3,"non_inconsistency"),EXACT(K3,"indeterminate")))),AND(AND(D3="retain",E3="protocol_report"),L3&lt;&gt;"",NOT(OR(EXACT(L3,"substantive_difference"),EXACT(L3,"minor_presentation"),EXACT(L3,"version_timing"),EXACT(L3,"non_inconsistency"),EXACT(L3,"indeterminate"))))),"CHECK FIELDS",IF(AND(F3&lt;&gt;"",NOT(OR(EXACT(F3,"no"),EXACT(F3,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F3,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H3" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4500,16 +4545,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L3" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L3" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
-      <c r="R3" s="9"/>
+      <c r="R3" s="9" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="91.95" customHeight="1">
       <c r="A4" s="3" t="s">
@@ -4521,16 +4567,18 @@
       <c r="C4" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D4" s="8"/>
+      <c r="D4" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E4" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A4="",COUNTIF($A$2:$A$20,A4)&lt;&gt;1,LEFT(A4,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D4="retain",E4="statistical_results")),H4&lt;&gt;"",NOT(EXACT(H4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),I4&lt;&gt;"",NOT(EXACT(I4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="statistical_results")),J4&lt;&gt;"",NOT(EXACT(J4,"not_applicable"))),AND(NOT(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material"))),K4&lt;&gt;"",NOT(EXACT(K4,"not_applicable"))),AND(NOT(AND(D4="retain",E4="protocol_report")),L4&lt;&gt;"",NOT(EXACT(L4,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D4,"retain"),EXACT(D4,"exclude"),EXACT(D4,"discuss"))),NOT(OR(EXACT(E4,"statistical_results"),EXACT(E4,"report_internal_inconsistency"),EXACT(E4,"plan_material"),EXACT(E4,"protocol_report"))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(H4,"confirmed_issue"),EXACT(H4,"probable_issue"),EXACT(H4,"not_issue"),EXACT(H4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),NOT(OR(EXACT(I4,"substantive"),EXACT(I4,"minor_presentation"),EXACT(I4,"indeterminate")))),AND(AND(D4="retain",E4="statistical_results"),J4&lt;&gt;"",NOT(OR(EXACT(J4,"direct"),EXACT(J4,"possible"),EXACT(J4,"unlikely"),EXACT(J4,"unknown")))),AND(AND(D4="retain",OR(E4="report_internal_inconsistency",E4="plan_material")),NOT(OR(EXACT(K4,"substantive_inconsistency"),EXACT(K4,"minor_presentation"),EXACT(K4,"non_inconsistency"),EXACT(K4,"indeterminate")))),AND(AND(D4="retain",E4="protocol_report"),L4&lt;&gt;"",NOT(OR(EXACT(L4,"substantive_difference"),EXACT(L4,"minor_presentation"),EXACT(L4,"version_timing"),EXACT(L4,"non_inconsistency"),EXACT(L4,"indeterminate"))))),"CHECK FIELDS",IF(AND(F4&lt;&gt;"",NOT(OR(EXACT(F4,"no"),EXACT(F4,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F4,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H4" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4548,16 +4596,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L4" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L4" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="R4" s="9"/>
+      <c r="R4" s="9" t="s">
+        <v>650</v>
+      </c>
     </row>
     <row r="5" spans="1:18" ht="91.95" customHeight="1">
       <c r="A5" s="1" t="s">
@@ -4569,16 +4618,18 @@
       <c r="C5" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E5" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G5" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A5="",COUNTIF($A$2:$A$20,A5)&lt;&gt;1,LEFT(A5,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D5="retain",E5="statistical_results")),H5&lt;&gt;"",NOT(EXACT(H5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),I5&lt;&gt;"",NOT(EXACT(I5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="statistical_results")),J5&lt;&gt;"",NOT(EXACT(J5,"not_applicable"))),AND(NOT(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material"))),K5&lt;&gt;"",NOT(EXACT(K5,"not_applicable"))),AND(NOT(AND(D5="retain",E5="protocol_report")),L5&lt;&gt;"",NOT(EXACT(L5,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D5,"retain"),EXACT(D5,"exclude"),EXACT(D5,"discuss"))),NOT(OR(EXACT(E5,"statistical_results"),EXACT(E5,"report_internal_inconsistency"),EXACT(E5,"plan_material"),EXACT(E5,"protocol_report"))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(H5,"confirmed_issue"),EXACT(H5,"probable_issue"),EXACT(H5,"not_issue"),EXACT(H5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),NOT(OR(EXACT(I5,"substantive"),EXACT(I5,"minor_presentation"),EXACT(I5,"indeterminate")))),AND(AND(D5="retain",E5="statistical_results"),J5&lt;&gt;"",NOT(OR(EXACT(J5,"direct"),EXACT(J5,"possible"),EXACT(J5,"unlikely"),EXACT(J5,"unknown")))),AND(AND(D5="retain",OR(E5="report_internal_inconsistency",E5="plan_material")),NOT(OR(EXACT(K5,"substantive_inconsistency"),EXACT(K5,"minor_presentation"),EXACT(K5,"non_inconsistency"),EXACT(K5,"indeterminate")))),AND(AND(D5="retain",E5="protocol_report"),L5&lt;&gt;"",NOT(OR(EXACT(L5,"substantive_difference"),EXACT(L5,"minor_presentation"),EXACT(L5,"version_timing"),EXACT(L5,"non_inconsistency"),EXACT(L5,"indeterminate"))))),"CHECK FIELDS",IF(AND(F5&lt;&gt;"",NOT(OR(EXACT(F5,"no"),EXACT(F5,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F5,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H5" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4596,16 +4647,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L5" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L5" s="9" t="s">
+        <v>518</v>
       </c>
       <c r="M5" s="1"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="4"/>
-      <c r="R5" s="9"/>
+      <c r="R5" s="9" t="s">
+        <v>652</v>
+      </c>
     </row>
     <row r="6" spans="1:18" ht="91.95" customHeight="1">
       <c r="A6" s="3" t="s">
@@ -4617,16 +4669,18 @@
       <c r="C6" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E6" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G6" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A6="",COUNTIF($A$2:$A$20,A6)&lt;&gt;1,LEFT(A6,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D6="retain",E6="statistical_results")),H6&lt;&gt;"",NOT(EXACT(H6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),I6&lt;&gt;"",NOT(EXACT(I6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="statistical_results")),J6&lt;&gt;"",NOT(EXACT(J6,"not_applicable"))),AND(NOT(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material"))),K6&lt;&gt;"",NOT(EXACT(K6,"not_applicable"))),AND(NOT(AND(D6="retain",E6="protocol_report")),L6&lt;&gt;"",NOT(EXACT(L6,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D6,"retain"),EXACT(D6,"exclude"),EXACT(D6,"discuss"))),NOT(OR(EXACT(E6,"statistical_results"),EXACT(E6,"report_internal_inconsistency"),EXACT(E6,"plan_material"),EXACT(E6,"protocol_report"))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(H6,"confirmed_issue"),EXACT(H6,"probable_issue"),EXACT(H6,"not_issue"),EXACT(H6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),NOT(OR(EXACT(I6,"substantive"),EXACT(I6,"minor_presentation"),EXACT(I6,"indeterminate")))),AND(AND(D6="retain",E6="statistical_results"),J6&lt;&gt;"",NOT(OR(EXACT(J6,"direct"),EXACT(J6,"possible"),EXACT(J6,"unlikely"),EXACT(J6,"unknown")))),AND(AND(D6="retain",OR(E6="report_internal_inconsistency",E6="plan_material")),NOT(OR(EXACT(K6,"substantive_inconsistency"),EXACT(K6,"minor_presentation"),EXACT(K6,"non_inconsistency"),EXACT(K6,"indeterminate")))),AND(AND(D6="retain",E6="protocol_report"),L6&lt;&gt;"",NOT(OR(EXACT(L6,"substantive_difference"),EXACT(L6,"minor_presentation"),EXACT(L6,"version_timing"),EXACT(L6,"non_inconsistency"),EXACT(L6,"indeterminate"))))),"CHECK FIELDS",IF(AND(F6&lt;&gt;"",NOT(OR(EXACT(F6,"no"),EXACT(F6,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F6,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H6" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4644,16 +4698,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L6" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L6" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
-      <c r="R6" s="9"/>
+      <c r="R6" s="9" t="s">
+        <v>654</v>
+      </c>
     </row>
     <row r="7" spans="1:18" ht="91.95" customHeight="1">
       <c r="A7" s="1" t="s">
@@ -4713,16 +4768,18 @@
       <c r="C8" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D8" s="8"/>
+      <c r="D8" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E8" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G8" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A8="",COUNTIF($A$2:$A$20,A8)&lt;&gt;1,LEFT(A8,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D8="retain",E8="statistical_results")),H8&lt;&gt;"",NOT(EXACT(H8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),I8&lt;&gt;"",NOT(EXACT(I8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="statistical_results")),J8&lt;&gt;"",NOT(EXACT(J8,"not_applicable"))),AND(NOT(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material"))),K8&lt;&gt;"",NOT(EXACT(K8,"not_applicable"))),AND(NOT(AND(D8="retain",E8="protocol_report")),L8&lt;&gt;"",NOT(EXACT(L8,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D8,"retain"),EXACT(D8,"exclude"),EXACT(D8,"discuss"))),NOT(OR(EXACT(E8,"statistical_results"),EXACT(E8,"report_internal_inconsistency"),EXACT(E8,"plan_material"),EXACT(E8,"protocol_report"))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(H8,"confirmed_issue"),EXACT(H8,"probable_issue"),EXACT(H8,"not_issue"),EXACT(H8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),NOT(OR(EXACT(I8,"substantive"),EXACT(I8,"minor_presentation"),EXACT(I8,"indeterminate")))),AND(AND(D8="retain",E8="statistical_results"),J8&lt;&gt;"",NOT(OR(EXACT(J8,"direct"),EXACT(J8,"possible"),EXACT(J8,"unlikely"),EXACT(J8,"unknown")))),AND(AND(D8="retain",OR(E8="report_internal_inconsistency",E8="plan_material")),NOT(OR(EXACT(K8,"substantive_inconsistency"),EXACT(K8,"minor_presentation"),EXACT(K8,"non_inconsistency"),EXACT(K8,"indeterminate")))),AND(AND(D8="retain",E8="protocol_report"),L8&lt;&gt;"",NOT(OR(EXACT(L8,"substantive_difference"),EXACT(L8,"minor_presentation"),EXACT(L8,"version_timing"),EXACT(L8,"non_inconsistency"),EXACT(L8,"indeterminate"))))),"CHECK FIELDS",IF(AND(F8&lt;&gt;"",NOT(OR(EXACT(F8,"no"),EXACT(F8,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F8,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H8" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4740,16 +4797,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L8" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L8" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M8" s="3"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
-      <c r="R8" s="9"/>
+      <c r="R8" s="9" t="s">
+        <v>645</v>
+      </c>
     </row>
     <row r="9" spans="1:18" ht="91.95" customHeight="1">
       <c r="A9" s="1" t="s">
@@ -4761,16 +4819,18 @@
       <c r="C9" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="D9" s="8"/>
+      <c r="D9" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E9" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G9" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A9="",COUNTIF($A$2:$A$20,A9)&lt;&gt;1,LEFT(A9,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D9="retain",E9="statistical_results")),H9&lt;&gt;"",NOT(EXACT(H9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),I9&lt;&gt;"",NOT(EXACT(I9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="statistical_results")),J9&lt;&gt;"",NOT(EXACT(J9,"not_applicable"))),AND(NOT(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material"))),K9&lt;&gt;"",NOT(EXACT(K9,"not_applicable"))),AND(NOT(AND(D9="retain",E9="protocol_report")),L9&lt;&gt;"",NOT(EXACT(L9,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D9,"retain"),EXACT(D9,"exclude"),EXACT(D9,"discuss"))),NOT(OR(EXACT(E9,"statistical_results"),EXACT(E9,"report_internal_inconsistency"),EXACT(E9,"plan_material"),EXACT(E9,"protocol_report"))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(H9,"confirmed_issue"),EXACT(H9,"probable_issue"),EXACT(H9,"not_issue"),EXACT(H9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),NOT(OR(EXACT(I9,"substantive"),EXACT(I9,"minor_presentation"),EXACT(I9,"indeterminate")))),AND(AND(D9="retain",E9="statistical_results"),J9&lt;&gt;"",NOT(OR(EXACT(J9,"direct"),EXACT(J9,"possible"),EXACT(J9,"unlikely"),EXACT(J9,"unknown")))),AND(AND(D9="retain",OR(E9="report_internal_inconsistency",E9="plan_material")),NOT(OR(EXACT(K9,"substantive_inconsistency"),EXACT(K9,"minor_presentation"),EXACT(K9,"non_inconsistency"),EXACT(K9,"indeterminate")))),AND(AND(D9="retain",E9="protocol_report"),L9&lt;&gt;"",NOT(OR(EXACT(L9,"substantive_difference"),EXACT(L9,"minor_presentation"),EXACT(L9,"version_timing"),EXACT(L9,"non_inconsistency"),EXACT(L9,"indeterminate"))))),"CHECK FIELDS",IF(AND(F9&lt;&gt;"",NOT(OR(EXACT(F9,"no"),EXACT(F9,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F9,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H9" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4788,16 +4848,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L9" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L9" s="9" t="s">
+        <v>526</v>
       </c>
       <c r="M9" s="1"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
-      <c r="R9" s="9"/>
+      <c r="R9" s="9" t="s">
+        <v>648</v>
+      </c>
     </row>
     <row r="10" spans="1:18" ht="91.95" customHeight="1">
       <c r="A10" s="3" t="s">
@@ -4809,16 +4870,18 @@
       <c r="C10" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="D10" s="8"/>
+      <c r="D10" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E10" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G10" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A10="",COUNTIF($A$2:$A$20,A10)&lt;&gt;1,LEFT(A10,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D10="retain",E10="statistical_results")),H10&lt;&gt;"",NOT(EXACT(H10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),I10&lt;&gt;"",NOT(EXACT(I10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="statistical_results")),J10&lt;&gt;"",NOT(EXACT(J10,"not_applicable"))),AND(NOT(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material"))),K10&lt;&gt;"",NOT(EXACT(K10,"not_applicable"))),AND(NOT(AND(D10="retain",E10="protocol_report")),L10&lt;&gt;"",NOT(EXACT(L10,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D10,"retain"),EXACT(D10,"exclude"),EXACT(D10,"discuss"))),NOT(OR(EXACT(E10,"statistical_results"),EXACT(E10,"report_internal_inconsistency"),EXACT(E10,"plan_material"),EXACT(E10,"protocol_report"))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(H10,"confirmed_issue"),EXACT(H10,"probable_issue"),EXACT(H10,"not_issue"),EXACT(H10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),NOT(OR(EXACT(I10,"substantive"),EXACT(I10,"minor_presentation"),EXACT(I10,"indeterminate")))),AND(AND(D10="retain",E10="statistical_results"),J10&lt;&gt;"",NOT(OR(EXACT(J10,"direct"),EXACT(J10,"possible"),EXACT(J10,"unlikely"),EXACT(J10,"unknown")))),AND(AND(D10="retain",OR(E10="report_internal_inconsistency",E10="plan_material")),NOT(OR(EXACT(K10,"substantive_inconsistency"),EXACT(K10,"minor_presentation"),EXACT(K10,"non_inconsistency"),EXACT(K10,"indeterminate")))),AND(AND(D10="retain",E10="protocol_report"),L10&lt;&gt;"",NOT(OR(EXACT(L10,"substantive_difference"),EXACT(L10,"minor_presentation"),EXACT(L10,"version_timing"),EXACT(L10,"non_inconsistency"),EXACT(L10,"indeterminate"))))),"CHECK FIELDS",IF(AND(F10&lt;&gt;"",NOT(OR(EXACT(F10,"no"),EXACT(F10,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F10,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H10" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4836,16 +4899,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L10" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L10" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
-      <c r="R10" s="9"/>
+      <c r="R10" s="9" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="11" spans="1:18" ht="91.95" customHeight="1">
       <c r="A11" s="1" t="s">
@@ -4857,16 +4921,18 @@
       <c r="C11" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="D11" s="8"/>
+      <c r="D11" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E11" s="8" t="s">
         <v>71</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G11" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A11="",COUNTIF($A$2:$A$20,A11)&lt;&gt;1,LEFT(A11,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D11="retain",E11="statistical_results")),H11&lt;&gt;"",NOT(EXACT(H11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),I11&lt;&gt;"",NOT(EXACT(I11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="statistical_results")),J11&lt;&gt;"",NOT(EXACT(J11,"not_applicable"))),AND(NOT(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material"))),K11&lt;&gt;"",NOT(EXACT(K11,"not_applicable"))),AND(NOT(AND(D11="retain",E11="protocol_report")),L11&lt;&gt;"",NOT(EXACT(L11,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D11,"retain"),EXACT(D11,"exclude"),EXACT(D11,"discuss"))),NOT(OR(EXACT(E11,"statistical_results"),EXACT(E11,"report_internal_inconsistency"),EXACT(E11,"plan_material"),EXACT(E11,"protocol_report"))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(H11,"confirmed_issue"),EXACT(H11,"probable_issue"),EXACT(H11,"not_issue"),EXACT(H11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),NOT(OR(EXACT(I11,"substantive"),EXACT(I11,"minor_presentation"),EXACT(I11,"indeterminate")))),AND(AND(D11="retain",E11="statistical_results"),J11&lt;&gt;"",NOT(OR(EXACT(J11,"direct"),EXACT(J11,"possible"),EXACT(J11,"unlikely"),EXACT(J11,"unknown")))),AND(AND(D11="retain",OR(E11="report_internal_inconsistency",E11="plan_material")),NOT(OR(EXACT(K11,"substantive_inconsistency"),EXACT(K11,"minor_presentation"),EXACT(K11,"non_inconsistency"),EXACT(K11,"indeterminate")))),AND(AND(D11="retain",E11="protocol_report"),L11&lt;&gt;"",NOT(OR(EXACT(L11,"substantive_difference"),EXACT(L11,"minor_presentation"),EXACT(L11,"version_timing"),EXACT(L11,"non_inconsistency"),EXACT(L11,"indeterminate"))))),"CHECK FIELDS",IF(AND(F11&lt;&gt;"",NOT(OR(EXACT(F11,"no"),EXACT(F11,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F11,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H11" s="8" t="str">
         <f t="shared" si="0"/>
@@ -4884,16 +4950,17 @@
         <f t="shared" si="3"/>
         <v>not_applicable</v>
       </c>
-      <c r="L11" s="9" t="str">
-        <f t="shared" si="4"/>
-        <v/>
+      <c r="L11" s="9" t="s">
+        <v>554</v>
       </c>
       <c r="M11" s="1"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
-      <c r="R11" s="9"/>
+      <c r="R11" s="9" t="s">
+        <v>655</v>
+      </c>
     </row>
     <row r="12" spans="1:18" ht="91.95" customHeight="1">
       <c r="A12" s="3" t="s">
@@ -5145,16 +5212,18 @@
       <c r="C17" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="D17" s="8"/>
+      <c r="D17" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E17" s="8" t="s">
         <v>81</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G17" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A17="",COUNTIF($A$2:$A$20,A17)&lt;&gt;1,LEFT(A17,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D17="retain",E17="statistical_results")),H17&lt;&gt;"",NOT(EXACT(H17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),I17&lt;&gt;"",NOT(EXACT(I17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="statistical_results")),J17&lt;&gt;"",NOT(EXACT(J17,"not_applicable"))),AND(NOT(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material"))),K17&lt;&gt;"",NOT(EXACT(K17,"not_applicable"))),AND(NOT(AND(D17="retain",E17="protocol_report")),L17&lt;&gt;"",NOT(EXACT(L17,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D17,"retain"),EXACT(D17,"exclude"),EXACT(D17,"discuss"))),NOT(OR(EXACT(E17,"statistical_results"),EXACT(E17,"report_internal_inconsistency"),EXACT(E17,"plan_material"),EXACT(E17,"protocol_report"))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(H17,"confirmed_issue"),EXACT(H17,"probable_issue"),EXACT(H17,"not_issue"),EXACT(H17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),NOT(OR(EXACT(I17,"substantive"),EXACT(I17,"minor_presentation"),EXACT(I17,"indeterminate")))),AND(AND(D17="retain",E17="statistical_results"),J17&lt;&gt;"",NOT(OR(EXACT(J17,"direct"),EXACT(J17,"possible"),EXACT(J17,"unlikely"),EXACT(J17,"unknown")))),AND(AND(D17="retain",OR(E17="report_internal_inconsistency",E17="plan_material")),NOT(OR(EXACT(K17,"substantive_inconsistency"),EXACT(K17,"minor_presentation"),EXACT(K17,"non_inconsistency"),EXACT(K17,"indeterminate")))),AND(AND(D17="retain",E17="protocol_report"),L17&lt;&gt;"",NOT(OR(EXACT(L17,"substantive_difference"),EXACT(L17,"minor_presentation"),EXACT(L17,"version_timing"),EXACT(L17,"non_inconsistency"),EXACT(L17,"indeterminate"))))),"CHECK FIELDS",IF(AND(F17&lt;&gt;"",NOT(OR(EXACT(F17,"no"),EXACT(F17,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F17,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
+        <v>PRIMARY READY</v>
       </c>
       <c r="H17" s="8" t="str">
         <f t="shared" si="0"/>
@@ -5168,9 +5237,8 @@
         <f t="shared" si="2"/>
         <v>not_applicable</v>
       </c>
-      <c r="K17" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="K17" s="8" t="s">
+        <v>526</v>
       </c>
       <c r="L17" s="9" t="str">
         <f t="shared" si="4"/>
@@ -5181,7 +5249,9 @@
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
-      <c r="R17" s="9"/>
+      <c r="R17" s="9" t="s">
+        <v>656</v>
+      </c>
     </row>
     <row r="18" spans="1:18" ht="91.95" customHeight="1">
       <c r="A18" s="3" t="s">
@@ -5193,28 +5263,27 @@
       <c r="C18" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="D18" s="8"/>
+      <c r="D18" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E18" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G18" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A18="",COUNTIF($A$2:$A$20,A18)&lt;&gt;1,LEFT(A18,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D18="retain",E18="statistical_results")),H18&lt;&gt;"",NOT(EXACT(H18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),I18&lt;&gt;"",NOT(EXACT(I18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="statistical_results")),J18&lt;&gt;"",NOT(EXACT(J18,"not_applicable"))),AND(NOT(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material"))),K18&lt;&gt;"",NOT(EXACT(K18,"not_applicable"))),AND(NOT(AND(D18="retain",E18="protocol_report")),L18&lt;&gt;"",NOT(EXACT(L18,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D18,"retain"),EXACT(D18,"exclude"),EXACT(D18,"discuss"))),NOT(OR(EXACT(E18,"statistical_results"),EXACT(E18,"report_internal_inconsistency"),EXACT(E18,"plan_material"),EXACT(E18,"protocol_report"))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(H18,"confirmed_issue"),EXACT(H18,"probable_issue"),EXACT(H18,"not_issue"),EXACT(H18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),NOT(OR(EXACT(I18,"substantive"),EXACT(I18,"minor_presentation"),EXACT(I18,"indeterminate")))),AND(AND(D18="retain",E18="statistical_results"),J18&lt;&gt;"",NOT(OR(EXACT(J18,"direct"),EXACT(J18,"possible"),EXACT(J18,"unlikely"),EXACT(J18,"unknown")))),AND(AND(D18="retain",OR(E18="report_internal_inconsistency",E18="plan_material")),NOT(OR(EXACT(K18,"substantive_inconsistency"),EXACT(K18,"minor_presentation"),EXACT(K18,"non_inconsistency"),EXACT(K18,"indeterminate")))),AND(AND(D18="retain",E18="protocol_report"),L18&lt;&gt;"",NOT(OR(EXACT(L18,"substantive_difference"),EXACT(L18,"minor_presentation"),EXACT(L18,"version_timing"),EXACT(L18,"non_inconsistency"),EXACT(L18,"indeterminate"))))),"CHECK FIELDS",IF(AND(F18&lt;&gt;"",NOT(OR(EXACT(F18,"no"),EXACT(F18,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F18,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H18" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I18" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J18" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>536</v>
       </c>
       <c r="K18" s="8" t="str">
         <f t="shared" si="3"/>
@@ -5229,7 +5298,9 @@
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
-      <c r="R18" s="9"/>
+      <c r="R18" s="9" t="s">
+        <v>653</v>
+      </c>
     </row>
     <row r="19" spans="1:18" ht="91.95" customHeight="1">
       <c r="A19" s="1" t="s">
@@ -5241,28 +5312,27 @@
       <c r="C19" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="D19" s="8"/>
+      <c r="D19" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E19" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G19" s="1" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A19="",COUNTIF($A$2:$A$20,A19)&lt;&gt;1,LEFT(A19,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D19="retain",E19="statistical_results")),H19&lt;&gt;"",NOT(EXACT(H19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),I19&lt;&gt;"",NOT(EXACT(I19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="statistical_results")),J19&lt;&gt;"",NOT(EXACT(J19,"not_applicable"))),AND(NOT(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material"))),K19&lt;&gt;"",NOT(EXACT(K19,"not_applicable"))),AND(NOT(AND(D19="retain",E19="protocol_report")),L19&lt;&gt;"",NOT(EXACT(L19,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D19,"retain"),EXACT(D19,"exclude"),EXACT(D19,"discuss"))),NOT(OR(EXACT(E19,"statistical_results"),EXACT(E19,"report_internal_inconsistency"),EXACT(E19,"plan_material"),EXACT(E19,"protocol_report"))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(H19,"confirmed_issue"),EXACT(H19,"probable_issue"),EXACT(H19,"not_issue"),EXACT(H19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),NOT(OR(EXACT(I19,"substantive"),EXACT(I19,"minor_presentation"),EXACT(I19,"indeterminate")))),AND(AND(D19="retain",E19="statistical_results"),J19&lt;&gt;"",NOT(OR(EXACT(J19,"direct"),EXACT(J19,"possible"),EXACT(J19,"unlikely"),EXACT(J19,"unknown")))),AND(AND(D19="retain",OR(E19="report_internal_inconsistency",E19="plan_material")),NOT(OR(EXACT(K19,"substantive_inconsistency"),EXACT(K19,"minor_presentation"),EXACT(K19,"non_inconsistency"),EXACT(K19,"indeterminate")))),AND(AND(D19="retain",E19="protocol_report"),L19&lt;&gt;"",NOT(OR(EXACT(L19,"substantive_difference"),EXACT(L19,"minor_presentation"),EXACT(L19,"version_timing"),EXACT(L19,"non_inconsistency"),EXACT(L19,"indeterminate"))))),"CHECK FIELDS",IF(AND(F19&lt;&gt;"",NOT(OR(EXACT(F19,"no"),EXACT(F19,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F19,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H19" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I19" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J19" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="K19" s="8" t="str">
         <f t="shared" si="3"/>
@@ -5277,7 +5347,9 @@
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
-      <c r="R19" s="9"/>
+      <c r="R19" s="9" t="s">
+        <v>649</v>
+      </c>
     </row>
     <row r="20" spans="1:18" ht="91.95" customHeight="1">
       <c r="A20" s="3" t="s">
@@ -5289,28 +5361,27 @@
       <c r="C20" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="D20" s="8"/>
+      <c r="D20" s="8" t="s">
+        <v>485</v>
+      </c>
       <c r="E20" s="8" t="s">
         <v>66</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>67</v>
+        <v>570</v>
       </c>
       <c r="G20" s="3" t="str">
         <f>IFERROR(IF(LEN(TRIM(CLEAN(SUBSTITUTE(Setup!$B$2,CHAR(160)," "))))=0,"CHECK REVIEWER ID",IF(OR(A20="",COUNTIF($A$2:$A$20,A20)&lt;&gt;1,LEFT(A20,LEN("2025::jama.2025.20765::"))&lt;&gt;"2025::jama.2025.20765::"),"CHECK KEY",IF(OR(AND(NOT(AND(D20="retain",E20="statistical_results")),H20&lt;&gt;"",NOT(EXACT(H20,"not_applicable"))),AND(NOT(AND(D20="retain",E20="statistical_results")),I20&lt;&gt;"",NOT(EXACT(I20,"not_applicable"))),AND(NOT(AND(D20="retain",E20="statistical_results")),J20&lt;&gt;"",NOT(EXACT(J20,"not_applicable"))),AND(NOT(AND(D20="retain",OR(E20="report_internal_inconsistency",E20="plan_material"))),K20&lt;&gt;"",NOT(EXACT(K20,"not_applicable"))),AND(NOT(AND(D20="retain",E20="protocol_report")),L20&lt;&gt;"",NOT(EXACT(L20,"not_applicable")))),"CLEAR INACTIVE VALUES",IF(OR(NOT(OR(EXACT(D20,"retain"),EXACT(D20,"exclude"),EXACT(D20,"discuss"))),NOT(OR(EXACT(E20,"statistical_results"),EXACT(E20,"report_internal_inconsistency"),EXACT(E20,"plan_material"),EXACT(E20,"protocol_report"))),AND(AND(D20="retain",E20="statistical_results"),NOT(OR(EXACT(H20,"confirmed_issue"),EXACT(H20,"probable_issue"),EXACT(H20,"not_issue"),EXACT(H20,"indeterminate")))),AND(AND(D20="retain",E20="statistical_results"),NOT(OR(EXACT(I20,"substantive"),EXACT(I20,"minor_presentation"),EXACT(I20,"indeterminate")))),AND(AND(D20="retain",E20="statistical_results"),J20&lt;&gt;"",NOT(OR(EXACT(J20,"direct"),EXACT(J20,"possible"),EXACT(J20,"unlikely"),EXACT(J20,"unknown")))),AND(AND(D20="retain",OR(E20="report_internal_inconsistency",E20="plan_material")),NOT(OR(EXACT(K20,"substantive_inconsistency"),EXACT(K20,"minor_presentation"),EXACT(K20,"non_inconsistency"),EXACT(K20,"indeterminate")))),AND(AND(D20="retain",E20="protocol_report"),L20&lt;&gt;"",NOT(OR(EXACT(L20,"substantive_difference"),EXACT(L20,"minor_presentation"),EXACT(L20,"version_timing"),EXACT(L20,"non_inconsistency"),EXACT(L20,"indeterminate"))))),"CHECK FIELDS",IF(AND(F20&lt;&gt;"",NOT(OR(EXACT(F20,"no"),EXACT(F20,"primary_done")))),"CHECK COMPLETE",IF(EXACT(F20,"primary_done"),"PRIMARY READY","PRIMARY DRAFT")))))),"CHECK INPUT / KEY")</f>
-        <v>CHECK FIELDS</v>
-      </c>
-      <c r="H20" s="8" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="I20" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J20" s="9" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>PRIMARY READY</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>534</v>
       </c>
       <c r="K20" s="8" t="str">
         <f t="shared" si="3"/>
@@ -5325,7 +5396,9 @@
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
-      <c r="R20" s="9"/>
+      <c r="R20" s="9" t="s">
+        <v>646</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R20" xr:uid="{00000000-0009-0000-0000-00000B000000}"/>
@@ -8936,7 +9009,7 @@
       </c>
       <c r="B4" s="6">
         <f>COUNTIF('C_jama.2024.24764'!$G$2:$G$6,"PRIMARY READY")+COUNTIF('C_jama.2024.27643'!$G$2:$G$17,"PRIMARY READY")+COUNTIF('C_jama.2025.11178'!$G$2:$G$19,"PRIMARY READY")+COUNTIF('C_jama.2025.15185'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.15440'!$G$2:$G$2,"PRIMARY READY")+COUNTIF('C_jama.2025.16450'!$G$2:$G$7,"PRIMARY READY")+COUNTIF('C_jama.2025.19563'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.19843'!$G$2:$G$8,"PRIMARY READY")+COUNTIF('C_jama.2025.20765'!$G$2:$G$20,"PRIMARY READY")+COUNTIF('C_jama.2025.24175'!$G$2:$G$15,"PRIMARY READY")+COUNTIF('C_jama.2025.4390'!$G$2:$G$14,"PRIMARY READY")+COUNTIF('C_jama.2025.7583'!$G$2:$G$5,"PRIMARY READY")+COUNTIF('C_jama.2025.7710'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9110'!$G$2:$G$4,"PRIMARY READY")+COUNTIF('C_jama.2025.9663'!$G$2:$G$6,"PRIMARY READY")</f>
-        <v>72</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="55.05" customHeight="1">
@@ -8954,7 +9027,7 @@
       </c>
       <c r="B6" s="6">
         <f>B3-B4</f>
-        <v>61</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="55.05" customHeight="1">
